--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934249</v>
+        <v>119934217</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536683</v>
+        <v>536771</v>
       </c>
       <c r="R7" t="n">
-        <v>7204683</v>
+        <v>7204791</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,6 +1341,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934217</v>
+        <v>119934079</v>
       </c>
       <c r="B8" t="n">
-        <v>90576</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536771</v>
+        <v>536847</v>
       </c>
       <c r="R8" t="n">
-        <v>7204791</v>
+        <v>7204825</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,21 +1468,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934079</v>
+        <v>119934249</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,21 +1500,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536847</v>
+        <v>536683</v>
       </c>
       <c r="R9" t="n">
-        <v>7204825</v>
+        <v>7204683</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -4465,10 +4465,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934081</v>
+        <v>119934114</v>
       </c>
       <c r="B35" t="n">
-        <v>79608</v>
+        <v>94323</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4477,25 +4477,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>2813</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536882</v>
+        <v>536852</v>
       </c>
       <c r="R35" t="n">
-        <v>7204819</v>
+        <v>7204836</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4577,10 +4577,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934114</v>
+        <v>119934081</v>
       </c>
       <c r="B36" t="n">
-        <v>94323</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4589,25 +4589,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536852</v>
+        <v>536882</v>
       </c>
       <c r="R36" t="n">
-        <v>7204836</v>
+        <v>7204819</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -4465,10 +4465,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934114</v>
+        <v>119934081</v>
       </c>
       <c r="B35" t="n">
-        <v>94323</v>
+        <v>79608</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4477,25 +4477,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536852</v>
+        <v>536882</v>
       </c>
       <c r="R35" t="n">
-        <v>7204836</v>
+        <v>7204819</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4577,10 +4577,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934081</v>
+        <v>119934114</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
+        <v>94323</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4589,25 +4589,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>2813</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536882</v>
+        <v>536852</v>
       </c>
       <c r="R36" t="n">
-        <v>7204819</v>
+        <v>7204836</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4689,10 +4689,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934248</v>
+        <v>119934066</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>90509</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4705,21 +4705,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536694</v>
+        <v>536771</v>
       </c>
       <c r="R37" t="n">
-        <v>7204667</v>
+        <v>7204791</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4785,6 +4785,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5029,10 +5044,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934066</v>
+        <v>119934248</v>
       </c>
       <c r="B40" t="n">
-        <v>90509</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5045,21 +5060,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5069,10 +5084,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536771</v>
+        <v>536694</v>
       </c>
       <c r="R40" t="n">
-        <v>7204791</v>
+        <v>7204667</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5104,7 +5119,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5114,7 +5129,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5125,21 +5140,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934245</v>
+        <v>119934014</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536407</v>
+        <v>536418</v>
       </c>
       <c r="R2" t="n">
-        <v>7204331</v>
+        <v>7204363</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934203</v>
+        <v>119934245</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536405</v>
+        <v>536407</v>
       </c>
       <c r="R3" t="n">
-        <v>7204335</v>
+        <v>7204331</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934015</v>
+        <v>119934203</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536441</v>
+        <v>536405</v>
       </c>
       <c r="R4" t="n">
-        <v>7204337</v>
+        <v>7204335</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934014</v>
+        <v>119934015</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1052,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536418</v>
+        <v>536441</v>
       </c>
       <c r="R5" t="n">
-        <v>7204363</v>
+        <v>7204337</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934217</v>
+        <v>119934078</v>
       </c>
       <c r="B7" t="n">
-        <v>90576</v>
+        <v>79608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536771</v>
+        <v>536606</v>
       </c>
       <c r="R7" t="n">
-        <v>7204791</v>
+        <v>7204748</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,21 +1341,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1372,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934079</v>
+        <v>119934062</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536847</v>
+        <v>536865</v>
       </c>
       <c r="R8" t="n">
-        <v>7204825</v>
+        <v>7204832</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934249</v>
+        <v>119934214</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536683</v>
+        <v>536641</v>
       </c>
       <c r="R9" t="n">
-        <v>7204683</v>
+        <v>7204731</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934137</v>
+        <v>119934218</v>
       </c>
       <c r="B10" t="n">
-        <v>74643</v>
+        <v>90576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536837</v>
+        <v>536789</v>
       </c>
       <c r="R10" t="n">
-        <v>7204821</v>
+        <v>7204793</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,6 +1677,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1708,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934030</v>
+        <v>119934184</v>
       </c>
       <c r="B11" t="n">
-        <v>56522</v>
+        <v>94311</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,38 +1724,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536532</v>
+        <v>536806</v>
       </c>
       <c r="R11" t="n">
-        <v>7204362</v>
+        <v>7204783</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934215</v>
+        <v>119934114</v>
       </c>
       <c r="B12" t="n">
-        <v>90576</v>
+        <v>94323</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,25 +1832,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>2813</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1864,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536591</v>
+        <v>536852</v>
       </c>
       <c r="R12" t="n">
-        <v>7204751</v>
+        <v>7204836</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934210</v>
+        <v>119934246</v>
       </c>
       <c r="B13" t="n">
-        <v>74622</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,25 +1944,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1976,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536837</v>
+        <v>536532</v>
       </c>
       <c r="R13" t="n">
-        <v>7204821</v>
+        <v>7204362</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2011,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934250</v>
+        <v>119934052</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>91339</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,25 +2056,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>918</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2088,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536603</v>
+        <v>536807</v>
       </c>
       <c r="R14" t="n">
-        <v>7204748</v>
+        <v>7204778</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2123,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,6 +2140,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2160,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934062</v>
+        <v>119934216</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>90576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,25 +2183,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2200,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536865</v>
+        <v>536769</v>
       </c>
       <c r="R15" t="n">
-        <v>7204832</v>
+        <v>7204825</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2235,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2245,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,6 +2267,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2272,7 +2298,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934253</v>
+        <v>119934252</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2312,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536884</v>
+        <v>536859</v>
       </c>
       <c r="R16" t="n">
-        <v>7204818</v>
+        <v>7204833</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2347,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,10 +2410,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934252</v>
+        <v>119934137</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>74643</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,21 +2426,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2424,10 +2450,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536859</v>
+        <v>536837</v>
       </c>
       <c r="R17" t="n">
-        <v>7204833</v>
+        <v>7204821</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2459,7 +2485,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,7 +2495,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,7 +2522,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934078</v>
+        <v>119934081</v>
       </c>
       <c r="B18" t="n">
         <v>79608</v>
@@ -2536,10 +2562,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536606</v>
+        <v>536882</v>
       </c>
       <c r="R18" t="n">
-        <v>7204748</v>
+        <v>7204819</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2571,7 +2597,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,7 +2607,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,10 +2634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934246</v>
+        <v>119934079</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,21 +2650,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2648,10 +2674,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536532</v>
+        <v>536847</v>
       </c>
       <c r="R19" t="n">
-        <v>7204362</v>
+        <v>7204825</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2683,7 +2709,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2693,7 +2719,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119933991</v>
+        <v>119934251</v>
       </c>
       <c r="B20" t="n">
-        <v>86057</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,25 +2758,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3294</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2786,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536861</v>
+        <v>536625</v>
       </c>
       <c r="R20" t="n">
-        <v>7204835</v>
+        <v>7204790</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,7 +2821,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,7 +2831,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,6 +2842,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2832,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934216</v>
+        <v>119934248</v>
       </c>
       <c r="B21" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,21 +2889,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2872,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536769</v>
+        <v>536694</v>
       </c>
       <c r="R21" t="n">
-        <v>7204825</v>
+        <v>7204667</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2907,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2958,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,21 +2969,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2959,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934247</v>
+        <v>119934004</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,21 +3001,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2999,10 +3025,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536691</v>
+        <v>536620</v>
       </c>
       <c r="R22" t="n">
-        <v>7204650</v>
+        <v>7204779</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3034,7 +3060,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,7 +3070,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,6 +3081,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3071,10 +3102,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934080</v>
+        <v>119934065</v>
       </c>
       <c r="B23" t="n">
-        <v>79608</v>
+        <v>90509</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,21 +3118,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>112</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3111,10 +3142,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536865</v>
+        <v>536683</v>
       </c>
       <c r="R23" t="n">
-        <v>7204832</v>
+        <v>7204683</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3146,7 +3177,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,7 +3187,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,7 +3214,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934214</v>
+        <v>119934217</v>
       </c>
       <c r="B24" t="n">
         <v>90576</v>
@@ -3223,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536641</v>
+        <v>536771</v>
       </c>
       <c r="R24" t="n">
-        <v>7204731</v>
+        <v>7204791</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3258,7 +3289,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3268,7 +3299,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3279,6 +3310,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3295,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934251</v>
+        <v>119934208</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3311,21 +3357,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3335,10 +3381,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536625</v>
+        <v>536690</v>
       </c>
       <c r="R25" t="n">
-        <v>7204790</v>
+        <v>7204670</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3370,7 +3416,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3426,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3391,21 +3437,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3422,10 +3453,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934184</v>
+        <v>119934249</v>
       </c>
       <c r="B26" t="n">
-        <v>94311</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3434,25 +3465,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3462,10 +3493,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536806</v>
+        <v>536683</v>
       </c>
       <c r="R26" t="n">
-        <v>7204783</v>
+        <v>7204683</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3497,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,10 +3565,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934221</v>
+        <v>119934016</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3550,34 +3581,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536697</v>
+        <v>536575</v>
       </c>
       <c r="R27" t="n">
-        <v>7204666</v>
+        <v>7204458</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3609,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3619,7 +3655,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,10 +3682,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934194</v>
+        <v>119934210</v>
       </c>
       <c r="B28" t="n">
-        <v>79643</v>
+        <v>74622</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3662,21 +3698,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3686,10 +3722,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536627</v>
+        <v>536837</v>
       </c>
       <c r="R28" t="n">
-        <v>7204789</v>
+        <v>7204821</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3721,7 +3757,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3731,7 +3767,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,10 +3794,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934016</v>
+        <v>119934194</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,43 +3806,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536575</v>
+        <v>536627</v>
       </c>
       <c r="R29" t="n">
-        <v>7204458</v>
+        <v>7204789</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3838,7 +3869,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3879,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934064</v>
+        <v>119934066</v>
       </c>
       <c r="B30" t="n">
-        <v>97074</v>
+        <v>90509</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3887,25 +3918,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220250</v>
+        <v>112</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3915,10 +3946,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536851</v>
+        <v>536771</v>
       </c>
       <c r="R30" t="n">
-        <v>7204845</v>
+        <v>7204791</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3950,7 +3981,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3960,7 +3991,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,6 +4002,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3987,10 +4033,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934218</v>
+        <v>119934041</v>
       </c>
       <c r="B31" t="n">
-        <v>90576</v>
+        <v>57463</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4003,34 +4049,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536789</v>
+        <v>536542</v>
       </c>
       <c r="R31" t="n">
-        <v>7204793</v>
+        <v>7204366</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4062,7 +4112,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4072,7 +4122,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4083,21 +4133,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4114,10 +4149,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934052</v>
+        <v>119934247</v>
       </c>
       <c r="B32" t="n">
-        <v>91339</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4126,25 +4161,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>918</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4154,10 +4189,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536807</v>
+        <v>536691</v>
       </c>
       <c r="R32" t="n">
-        <v>7204778</v>
+        <v>7204650</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4189,7 +4224,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4199,7 +4234,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4210,21 +4245,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4241,10 +4261,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934207</v>
+        <v>119934064</v>
       </c>
       <c r="B33" t="n">
-        <v>90558</v>
+        <v>97074</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4253,25 +4273,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>220250</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4281,10 +4301,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536704</v>
+        <v>536851</v>
       </c>
       <c r="R33" t="n">
-        <v>7204580</v>
+        <v>7204845</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4316,7 +4336,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4326,7 +4346,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4353,10 +4373,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934065</v>
+        <v>119934080</v>
       </c>
       <c r="B34" t="n">
-        <v>90509</v>
+        <v>79608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4369,21 +4389,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4393,10 +4413,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536683</v>
+        <v>536865</v>
       </c>
       <c r="R34" t="n">
-        <v>7204683</v>
+        <v>7204832</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4428,7 +4448,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4438,7 +4458,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4465,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934081</v>
+        <v>119934250</v>
       </c>
       <c r="B35" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4481,21 +4501,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4505,10 +4525,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536882</v>
+        <v>536603</v>
       </c>
       <c r="R35" t="n">
-        <v>7204819</v>
+        <v>7204748</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4540,7 +4560,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4550,7 +4570,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4577,10 +4597,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934114</v>
+        <v>119934030</v>
       </c>
       <c r="B36" t="n">
-        <v>94323</v>
+        <v>56522</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4593,34 +4613,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2813</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536852</v>
+        <v>536532</v>
       </c>
       <c r="R36" t="n">
-        <v>7204836</v>
+        <v>7204362</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4652,7 +4676,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4662,7 +4686,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4689,10 +4713,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934066</v>
+        <v>119934221</v>
       </c>
       <c r="B37" t="n">
-        <v>90509</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4705,21 +4729,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4729,10 +4753,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536771</v>
+        <v>536697</v>
       </c>
       <c r="R37" t="n">
-        <v>7204791</v>
+        <v>7204666</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4764,7 +4788,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4774,7 +4798,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4785,21 +4809,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4816,10 +4825,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934041</v>
+        <v>119934207</v>
       </c>
       <c r="B38" t="n">
-        <v>57463</v>
+        <v>90558</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4832,38 +4841,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536542</v>
+        <v>536704</v>
       </c>
       <c r="R38" t="n">
-        <v>7204366</v>
+        <v>7204580</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4895,7 +4900,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4905,7 +4910,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4932,10 +4937,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934208</v>
+        <v>119934253</v>
       </c>
       <c r="B39" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4948,21 +4953,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4972,10 +4977,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536690</v>
+        <v>536884</v>
       </c>
       <c r="R39" t="n">
-        <v>7204670</v>
+        <v>7204818</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5007,7 +5012,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5017,7 +5022,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5044,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934248</v>
+        <v>119934215</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5060,21 +5065,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5084,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536694</v>
+        <v>536591</v>
       </c>
       <c r="R40" t="n">
-        <v>7204667</v>
+        <v>7204751</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5119,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5129,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5156,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934004</v>
+        <v>119933991</v>
       </c>
       <c r="B41" t="n">
-        <v>89633</v>
+        <v>86057</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5168,25 +5173,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1962</v>
+        <v>3294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5196,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536620</v>
+        <v>536861</v>
       </c>
       <c r="R41" t="n">
-        <v>7204779</v>
+        <v>7204835</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5231,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5241,7 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5252,11 +5257,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934078</v>
+        <v>119934062</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536606</v>
+        <v>536865</v>
       </c>
       <c r="R7" t="n">
-        <v>7204748</v>
+        <v>7204832</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934062</v>
+        <v>119934078</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536865</v>
+        <v>536606</v>
       </c>
       <c r="R8" t="n">
-        <v>7204832</v>
+        <v>7204748</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934214</v>
+        <v>119934184</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>94311</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536641</v>
+        <v>536806</v>
       </c>
       <c r="R9" t="n">
-        <v>7204731</v>
+        <v>7204783</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934218</v>
+        <v>119934114</v>
       </c>
       <c r="B10" t="n">
-        <v>90576</v>
+        <v>94323</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1593,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536789</v>
+        <v>536852</v>
       </c>
       <c r="R10" t="n">
-        <v>7204793</v>
+        <v>7204836</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,21 +1677,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1708,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934184</v>
+        <v>119934246</v>
       </c>
       <c r="B11" t="n">
-        <v>94311</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536806</v>
+        <v>536532</v>
       </c>
       <c r="R11" t="n">
-        <v>7204783</v>
+        <v>7204362</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934114</v>
+        <v>119934214</v>
       </c>
       <c r="B12" t="n">
-        <v>94323</v>
+        <v>90576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,25 +1817,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2813</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536852</v>
+        <v>536641</v>
       </c>
       <c r="R12" t="n">
-        <v>7204836</v>
+        <v>7204731</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934246</v>
+        <v>119934218</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,21 +1933,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536532</v>
+        <v>536789</v>
       </c>
       <c r="R13" t="n">
-        <v>7204362</v>
+        <v>7204793</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,6 +2013,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -4033,10 +4033,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934041</v>
+        <v>119934064</v>
       </c>
       <c r="B31" t="n">
-        <v>57463</v>
+        <v>97074</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4045,42 +4045,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220250</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536542</v>
+        <v>536851</v>
       </c>
       <c r="R31" t="n">
-        <v>7204366</v>
+        <v>7204845</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4112,7 +4108,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4122,7 +4118,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4261,10 +4257,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934064</v>
+        <v>119934041</v>
       </c>
       <c r="B33" t="n">
-        <v>97074</v>
+        <v>57463</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4273,38 +4269,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220250</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536851</v>
+        <v>536542</v>
       </c>
       <c r="R33" t="n">
-        <v>7204845</v>
+        <v>7204366</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5049,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934215</v>
+        <v>119933991</v>
       </c>
       <c r="B40" t="n">
-        <v>90576</v>
+        <v>86057</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5061,25 +5061,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>3294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536591</v>
+        <v>536861</v>
       </c>
       <c r="R40" t="n">
-        <v>7204751</v>
+        <v>7204835</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119933991</v>
+        <v>119934215</v>
       </c>
       <c r="B41" t="n">
-        <v>86057</v>
+        <v>90576</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5173,25 +5173,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3294</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536861</v>
+        <v>536591</v>
       </c>
       <c r="R41" t="n">
-        <v>7204835</v>
+        <v>7204751</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934014</v>
+        <v>119934203</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536418</v>
+        <v>536405</v>
       </c>
       <c r="R2" t="n">
-        <v>7204363</v>
+        <v>7204335</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934245</v>
+        <v>119934009</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536407</v>
+        <v>536410</v>
       </c>
       <c r="R3" t="n">
-        <v>7204331</v>
+        <v>7204341</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934203</v>
+        <v>119934014</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536405</v>
+        <v>536418</v>
       </c>
       <c r="R4" t="n">
-        <v>7204335</v>
+        <v>7204363</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934009</v>
+        <v>119934245</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536410</v>
+        <v>536407</v>
       </c>
       <c r="R6" t="n">
-        <v>7204341</v>
+        <v>7204331</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934062</v>
+        <v>119933991</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>86057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>3294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536865</v>
+        <v>536861</v>
       </c>
       <c r="R7" t="n">
-        <v>7204832</v>
+        <v>7204835</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934078</v>
+        <v>119934251</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536606</v>
+        <v>536625</v>
       </c>
       <c r="R8" t="n">
-        <v>7204748</v>
+        <v>7204790</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,6 +1453,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1469,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934184</v>
+        <v>119934210</v>
       </c>
       <c r="B9" t="n">
-        <v>94311</v>
+        <v>74622</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1500,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536806</v>
+        <v>536837</v>
       </c>
       <c r="R9" t="n">
-        <v>7204783</v>
+        <v>7204821</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934114</v>
+        <v>119934080</v>
       </c>
       <c r="B10" t="n">
-        <v>94323</v>
+        <v>79608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536852</v>
+        <v>536865</v>
       </c>
       <c r="R10" t="n">
-        <v>7204836</v>
+        <v>7204832</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934246</v>
+        <v>119934216</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536532</v>
+        <v>536769</v>
       </c>
       <c r="R11" t="n">
-        <v>7204362</v>
+        <v>7204825</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,6 +1804,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1805,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934214</v>
+        <v>119934041</v>
       </c>
       <c r="B12" t="n">
-        <v>90576</v>
+        <v>57463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1851,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536641</v>
+        <v>536542</v>
       </c>
       <c r="R12" t="n">
-        <v>7204731</v>
+        <v>7204366</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1951,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934218</v>
+        <v>119934052</v>
       </c>
       <c r="B13" t="n">
-        <v>90576</v>
+        <v>91339</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1963,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>918</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536789</v>
+        <v>536807</v>
       </c>
       <c r="R13" t="n">
-        <v>7204793</v>
+        <v>7204778</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934052</v>
+        <v>119934214</v>
       </c>
       <c r="B14" t="n">
-        <v>91339</v>
+        <v>90576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,25 +2090,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>918</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2118,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536807</v>
+        <v>536641</v>
       </c>
       <c r="R14" t="n">
-        <v>7204778</v>
+        <v>7204731</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2153,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2163,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,21 +2174,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2171,10 +2190,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934216</v>
+        <v>119934208</v>
       </c>
       <c r="B15" t="n">
-        <v>90576</v>
+        <v>90558</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,21 +2206,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2211,10 +2230,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536769</v>
+        <v>536690</v>
       </c>
       <c r="R15" t="n">
-        <v>7204825</v>
+        <v>7204670</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2246,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,21 +2286,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2298,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934252</v>
+        <v>119934194</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,25 +2314,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2338,10 +2342,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536859</v>
+        <v>536627</v>
       </c>
       <c r="R16" t="n">
-        <v>7204833</v>
+        <v>7204789</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2373,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934137</v>
+        <v>119934252</v>
       </c>
       <c r="B17" t="n">
-        <v>74643</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2450,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536837</v>
+        <v>536859</v>
       </c>
       <c r="R17" t="n">
-        <v>7204821</v>
+        <v>7204833</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2485,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2495,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2522,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934081</v>
+        <v>119934246</v>
       </c>
       <c r="B18" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,21 +2542,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2562,10 +2566,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536882</v>
+        <v>536532</v>
       </c>
       <c r="R18" t="n">
-        <v>7204819</v>
+        <v>7204362</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2597,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2607,7 +2611,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,10 +2638,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934079</v>
+        <v>119934247</v>
       </c>
       <c r="B19" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2650,21 +2654,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2674,10 +2678,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536847</v>
+        <v>536691</v>
       </c>
       <c r="R19" t="n">
-        <v>7204825</v>
+        <v>7204650</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2709,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2719,7 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2746,7 +2750,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934251</v>
+        <v>119934253</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2786,10 +2790,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536625</v>
+        <v>536884</v>
       </c>
       <c r="R20" t="n">
-        <v>7204790</v>
+        <v>7204818</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2821,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2831,7 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,21 +2846,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2873,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934248</v>
+        <v>119934217</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,21 +2878,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2913,10 +2902,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536694</v>
+        <v>536771</v>
       </c>
       <c r="R21" t="n">
-        <v>7204667</v>
+        <v>7204791</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2948,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,6 +2958,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2985,10 +2989,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934004</v>
+        <v>119934081</v>
       </c>
       <c r="B22" t="n">
-        <v>89633</v>
+        <v>79608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,21 +3005,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3025,10 +3029,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536620</v>
+        <v>536882</v>
       </c>
       <c r="R22" t="n">
-        <v>7204779</v>
+        <v>7204819</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3060,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3070,7 +3074,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,11 +3085,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3102,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934065</v>
+        <v>119934250</v>
       </c>
       <c r="B23" t="n">
-        <v>90509</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3118,21 +3117,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3142,10 +3141,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536683</v>
+        <v>536603</v>
       </c>
       <c r="R23" t="n">
-        <v>7204683</v>
+        <v>7204748</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3177,7 +3176,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3187,7 +3186,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,10 +3213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934217</v>
+        <v>119934064</v>
       </c>
       <c r="B24" t="n">
-        <v>90576</v>
+        <v>97074</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3226,25 +3225,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>220250</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3254,10 +3253,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536771</v>
+        <v>536851</v>
       </c>
       <c r="R24" t="n">
-        <v>7204791</v>
+        <v>7204845</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3289,7 +3288,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3299,7 +3298,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,21 +3309,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3341,10 +3325,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934208</v>
+        <v>119934079</v>
       </c>
       <c r="B25" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3357,21 +3341,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,10 +3365,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536690</v>
+        <v>536847</v>
       </c>
       <c r="R25" t="n">
-        <v>7204670</v>
+        <v>7204825</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3416,7 +3400,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3426,7 +3410,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,10 +3549,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934016</v>
+        <v>119934248</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,39 +3565,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536575</v>
+        <v>536694</v>
       </c>
       <c r="R27" t="n">
-        <v>7204458</v>
+        <v>7204667</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3645,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,7 +3634,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3682,10 +3661,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934210</v>
+        <v>119934184</v>
       </c>
       <c r="B28" t="n">
-        <v>74622</v>
+        <v>94311</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,21 +3677,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3722,10 +3701,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536837</v>
+        <v>536806</v>
       </c>
       <c r="R28" t="n">
-        <v>7204821</v>
+        <v>7204783</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3757,7 +3736,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3767,7 +3746,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3794,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934194</v>
+        <v>119934137</v>
       </c>
       <c r="B29" t="n">
-        <v>79643</v>
+        <v>74643</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3806,25 +3785,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3834,10 +3813,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536627</v>
+        <v>536837</v>
       </c>
       <c r="R29" t="n">
-        <v>7204789</v>
+        <v>7204821</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3869,7 +3848,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3879,7 +3858,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3906,7 +3885,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934066</v>
+        <v>119934065</v>
       </c>
       <c r="B30" t="n">
         <v>90509</v>
@@ -3946,10 +3925,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536771</v>
+        <v>536683</v>
       </c>
       <c r="R30" t="n">
-        <v>7204791</v>
+        <v>7204683</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3981,7 +3960,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3991,7 +3970,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4002,21 +3981,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4033,10 +3997,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934064</v>
+        <v>119934218</v>
       </c>
       <c r="B31" t="n">
-        <v>97074</v>
+        <v>90576</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4045,25 +4009,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220250</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4073,10 +4037,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536851</v>
+        <v>536789</v>
       </c>
       <c r="R31" t="n">
-        <v>7204845</v>
+        <v>7204793</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4108,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4118,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4129,6 +4093,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4145,10 +4124,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934247</v>
+        <v>119934062</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4157,25 +4136,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4185,10 +4164,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536691</v>
+        <v>536865</v>
       </c>
       <c r="R32" t="n">
-        <v>7204650</v>
+        <v>7204832</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4220,7 +4199,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4230,7 +4209,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4257,10 +4236,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934041</v>
+        <v>119934030</v>
       </c>
       <c r="B33" t="n">
-        <v>57463</v>
+        <v>56522</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4269,30 +4248,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4301,10 +4280,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536542</v>
+        <v>536532</v>
       </c>
       <c r="R33" t="n">
-        <v>7204366</v>
+        <v>7204362</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4336,7 +4315,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4346,7 +4325,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4373,10 +4352,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934080</v>
+        <v>119934215</v>
       </c>
       <c r="B34" t="n">
-        <v>79608</v>
+        <v>90576</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4389,21 +4368,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4413,10 +4392,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536865</v>
+        <v>536591</v>
       </c>
       <c r="R34" t="n">
-        <v>7204832</v>
+        <v>7204751</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4448,7 +4427,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4458,7 +4437,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4485,10 +4464,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934250</v>
+        <v>119934114</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>94323</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4497,25 +4476,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4525,10 +4504,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536603</v>
+        <v>536852</v>
       </c>
       <c r="R35" t="n">
-        <v>7204748</v>
+        <v>7204836</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4560,7 +4539,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4570,7 +4549,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4597,10 +4576,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934030</v>
+        <v>119934016</v>
       </c>
       <c r="B36" t="n">
-        <v>56522</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4609,30 +4588,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4641,10 +4621,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536532</v>
+        <v>536575</v>
       </c>
       <c r="R36" t="n">
-        <v>7204362</v>
+        <v>7204458</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4676,7 +4656,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4686,7 +4666,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4713,10 +4693,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934221</v>
+        <v>119934078</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>79608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4729,21 +4709,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4753,10 +4733,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536697</v>
+        <v>536606</v>
       </c>
       <c r="R37" t="n">
-        <v>7204666</v>
+        <v>7204748</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4788,7 +4768,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4798,7 +4778,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4825,10 +4805,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934207</v>
+        <v>119934004</v>
       </c>
       <c r="B38" t="n">
-        <v>90558</v>
+        <v>89633</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4841,21 +4821,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>1962</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4865,10 +4845,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536704</v>
+        <v>536620</v>
       </c>
       <c r="R38" t="n">
-        <v>7204580</v>
+        <v>7204779</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4900,7 +4880,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4910,7 +4890,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4921,6 +4901,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4937,10 +4922,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934253</v>
+        <v>119934207</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4953,21 +4938,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4977,10 +4962,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536884</v>
+        <v>536704</v>
       </c>
       <c r="R39" t="n">
-        <v>7204818</v>
+        <v>7204580</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5012,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5022,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5049,10 +5034,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119933991</v>
+        <v>119934221</v>
       </c>
       <c r="B40" t="n">
-        <v>86057</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5061,25 +5046,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3294</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5074,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536861</v>
+        <v>536697</v>
       </c>
       <c r="R40" t="n">
-        <v>7204835</v>
+        <v>7204666</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5124,7 +5109,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5134,7 +5119,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,10 +5146,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934215</v>
+        <v>119934066</v>
       </c>
       <c r="B41" t="n">
-        <v>90576</v>
+        <v>90509</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5177,21 +5162,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5201,10 +5186,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536591</v>
+        <v>536771</v>
       </c>
       <c r="R41" t="n">
-        <v>7204751</v>
+        <v>7204791</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5236,7 +5221,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5246,7 +5231,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5257,6 +5242,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -3325,10 +3325,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934079</v>
+        <v>119934249</v>
       </c>
       <c r="B25" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536847</v>
+        <v>536683</v>
       </c>
       <c r="R25" t="n">
-        <v>7204825</v>
+        <v>7204683</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934249</v>
+        <v>119934079</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3453,21 +3453,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536683</v>
+        <v>536847</v>
       </c>
       <c r="R26" t="n">
-        <v>7204683</v>
+        <v>7204825</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934009</v>
+        <v>119934014</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536410</v>
+        <v>536418</v>
       </c>
       <c r="R3" t="n">
-        <v>7204341</v>
+        <v>7204363</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934014</v>
+        <v>119934245</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536418</v>
+        <v>536407</v>
       </c>
       <c r="R4" t="n">
-        <v>7204363</v>
+        <v>7204331</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934015</v>
+        <v>119934009</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536441</v>
+        <v>536410</v>
       </c>
       <c r="R5" t="n">
-        <v>7204337</v>
+        <v>7204341</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934245</v>
+        <v>119934015</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536407</v>
+        <v>536441</v>
       </c>
       <c r="R6" t="n">
-        <v>7204331</v>
+        <v>7204337</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119933991</v>
+        <v>119934004</v>
       </c>
       <c r="B7" t="n">
-        <v>86057</v>
+        <v>89633</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3294</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536861</v>
+        <v>536620</v>
       </c>
       <c r="R7" t="n">
-        <v>7204835</v>
+        <v>7204779</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,6 +1341,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934251</v>
+        <v>119933991</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>86057</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>3294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536625</v>
+        <v>536861</v>
       </c>
       <c r="R8" t="n">
-        <v>7204790</v>
+        <v>7204835</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,21 +1458,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1484,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934210</v>
+        <v>119934218</v>
       </c>
       <c r="B9" t="n">
-        <v>74622</v>
+        <v>90576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536837</v>
+        <v>536789</v>
       </c>
       <c r="R9" t="n">
-        <v>7204821</v>
+        <v>7204793</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,6 +1570,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934080</v>
+        <v>119934016</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1617,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536865</v>
+        <v>536575</v>
       </c>
       <c r="R10" t="n">
-        <v>7204832</v>
+        <v>7204458</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934216</v>
+        <v>119934251</v>
       </c>
       <c r="B11" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,21 +1734,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536769</v>
+        <v>536625</v>
       </c>
       <c r="R11" t="n">
-        <v>7204825</v>
+        <v>7204790</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934041</v>
+        <v>119934079</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>79608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,38 +1861,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536542</v>
+        <v>536847</v>
       </c>
       <c r="R12" t="n">
-        <v>7204366</v>
+        <v>7204825</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1914,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934052</v>
+        <v>119934249</v>
       </c>
       <c r="B13" t="n">
-        <v>91339</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,25 +1969,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>918</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536807</v>
+        <v>536683</v>
       </c>
       <c r="R13" t="n">
-        <v>7204778</v>
+        <v>7204683</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2026,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,21 +2053,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2078,10 +2069,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934214</v>
+        <v>119934247</v>
       </c>
       <c r="B14" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,21 +2085,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2118,10 +2109,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536641</v>
+        <v>536691</v>
       </c>
       <c r="R14" t="n">
-        <v>7204731</v>
+        <v>7204650</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2153,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2163,7 +2154,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934208</v>
+        <v>119934250</v>
       </c>
       <c r="B15" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,21 +2197,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2230,10 +2221,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536690</v>
+        <v>536603</v>
       </c>
       <c r="R15" t="n">
-        <v>7204670</v>
+        <v>7204748</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2265,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2275,7 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934194</v>
+        <v>119934246</v>
       </c>
       <c r="B16" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,25 +2305,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2342,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536627</v>
+        <v>536532</v>
       </c>
       <c r="R16" t="n">
-        <v>7204789</v>
+        <v>7204362</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2377,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934252</v>
+        <v>119934194</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,25 +2417,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2445,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536859</v>
+        <v>536627</v>
       </c>
       <c r="R17" t="n">
-        <v>7204833</v>
+        <v>7204789</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,7 +2480,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2490,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934246</v>
+        <v>119934065</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>90509</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,21 +2533,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2566,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536532</v>
+        <v>536683</v>
       </c>
       <c r="R18" t="n">
-        <v>7204362</v>
+        <v>7204683</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2601,7 +2592,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2602,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934247</v>
+        <v>119934137</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>74643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,21 +2645,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2678,10 +2669,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536691</v>
+        <v>536837</v>
       </c>
       <c r="R19" t="n">
-        <v>7204650</v>
+        <v>7204821</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2713,7 +2704,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2714,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2862,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934217</v>
+        <v>119934052</v>
       </c>
       <c r="B21" t="n">
-        <v>90576</v>
+        <v>91339</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,25 +2865,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>918</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2902,10 +2893,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536771</v>
+        <v>536807</v>
       </c>
       <c r="R21" t="n">
-        <v>7204791</v>
+        <v>7204778</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2937,7 +2928,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2938,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2989,10 +2980,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934081</v>
+        <v>119934215</v>
       </c>
       <c r="B22" t="n">
-        <v>79608</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3005,21 +2996,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3029,10 +3020,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536882</v>
+        <v>536591</v>
       </c>
       <c r="R22" t="n">
-        <v>7204819</v>
+        <v>7204751</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3064,7 +3055,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,7 +3065,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934250</v>
+        <v>119934062</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,25 +3104,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3141,10 +3132,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536603</v>
+        <v>536865</v>
       </c>
       <c r="R23" t="n">
-        <v>7204748</v>
+        <v>7204832</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3176,7 +3167,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3186,7 +3177,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,10 +3204,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934064</v>
+        <v>119934252</v>
       </c>
       <c r="B24" t="n">
-        <v>97074</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3225,25 +3216,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220250</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3253,10 +3244,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536851</v>
+        <v>536859</v>
       </c>
       <c r="R24" t="n">
-        <v>7204845</v>
+        <v>7204833</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3288,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3298,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3325,10 +3316,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934249</v>
+        <v>119934081</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3341,21 +3332,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3365,10 +3356,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536683</v>
+        <v>536882</v>
       </c>
       <c r="R25" t="n">
-        <v>7204683</v>
+        <v>7204819</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3400,7 +3391,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3410,7 +3401,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3437,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934079</v>
+        <v>119934217</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>90576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3453,21 +3444,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3477,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536847</v>
+        <v>536771</v>
       </c>
       <c r="R26" t="n">
-        <v>7204825</v>
+        <v>7204791</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3512,7 +3503,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,7 +3513,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,6 +3524,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3549,10 +3555,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934248</v>
+        <v>119934080</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,21 +3571,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3589,10 +3595,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536694</v>
+        <v>536865</v>
       </c>
       <c r="R27" t="n">
-        <v>7204667</v>
+        <v>7204832</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3624,7 +3630,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3634,7 +3640,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,10 +3667,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934184</v>
+        <v>119934064</v>
       </c>
       <c r="B28" t="n">
-        <v>94311</v>
+        <v>97074</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3677,21 +3683,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>220250</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3701,10 +3707,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536806</v>
+        <v>536851</v>
       </c>
       <c r="R28" t="n">
-        <v>7204783</v>
+        <v>7204845</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3736,7 +3742,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3746,7 +3752,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,10 +3779,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934137</v>
+        <v>119934248</v>
       </c>
       <c r="B29" t="n">
-        <v>74643</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3789,21 +3795,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3813,10 +3819,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536837</v>
+        <v>536694</v>
       </c>
       <c r="R29" t="n">
-        <v>7204821</v>
+        <v>7204667</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3848,7 +3854,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3858,7 +3864,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3891,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934065</v>
+        <v>119934184</v>
       </c>
       <c r="B30" t="n">
-        <v>90509</v>
+        <v>94311</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3897,25 +3903,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>112</v>
+        <v>2809</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3925,10 +3931,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536683</v>
+        <v>536806</v>
       </c>
       <c r="R30" t="n">
-        <v>7204683</v>
+        <v>7204783</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3960,7 +3966,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3970,7 +3976,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3997,10 +4003,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934218</v>
+        <v>119934114</v>
       </c>
       <c r="B31" t="n">
-        <v>90576</v>
+        <v>94323</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4009,25 +4015,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>2813</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4037,10 +4043,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536789</v>
+        <v>536852</v>
       </c>
       <c r="R31" t="n">
-        <v>7204793</v>
+        <v>7204836</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4072,7 +4078,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4088,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4093,21 +4099,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4124,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934062</v>
+        <v>119934216</v>
       </c>
       <c r="B32" t="n">
-        <v>79636</v>
+        <v>90576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4136,25 +4127,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4164,10 +4155,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536865</v>
+        <v>536769</v>
       </c>
       <c r="R32" t="n">
-        <v>7204832</v>
+        <v>7204825</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4199,7 +4190,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4209,7 +4200,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4220,6 +4211,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4236,10 +4242,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934030</v>
+        <v>119934041</v>
       </c>
       <c r="B33" t="n">
-        <v>56522</v>
+        <v>57463</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4248,30 +4254,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4280,10 +4286,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536532</v>
+        <v>536542</v>
       </c>
       <c r="R33" t="n">
-        <v>7204362</v>
+        <v>7204366</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4315,7 +4321,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4325,7 +4331,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4352,10 +4358,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934215</v>
+        <v>119934208</v>
       </c>
       <c r="B34" t="n">
-        <v>90576</v>
+        <v>90558</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4368,21 +4374,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4392,10 +4398,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536591</v>
+        <v>536690</v>
       </c>
       <c r="R34" t="n">
-        <v>7204751</v>
+        <v>7204670</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4427,7 +4433,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4437,7 +4443,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934114</v>
+        <v>119934210</v>
       </c>
       <c r="B35" t="n">
-        <v>94323</v>
+        <v>74622</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4480,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2813</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4504,10 +4510,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536852</v>
+        <v>536837</v>
       </c>
       <c r="R35" t="n">
-        <v>7204836</v>
+        <v>7204821</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4539,7 +4545,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4549,7 +4555,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4576,10 +4582,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934016</v>
+        <v>119934214</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4592,39 +4598,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536575</v>
+        <v>536641</v>
       </c>
       <c r="R36" t="n">
-        <v>7204458</v>
+        <v>7204731</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4656,7 +4657,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4666,7 +4667,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4693,10 +4694,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934078</v>
+        <v>119934030</v>
       </c>
       <c r="B37" t="n">
-        <v>79608</v>
+        <v>56522</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4705,38 +4706,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536606</v>
+        <v>536532</v>
       </c>
       <c r="R37" t="n">
-        <v>7204748</v>
+        <v>7204362</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4768,7 +4773,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4778,7 +4783,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4805,10 +4810,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934004</v>
+        <v>119934221</v>
       </c>
       <c r="B38" t="n">
-        <v>89633</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4821,21 +4826,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1962</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4845,10 +4850,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536620</v>
+        <v>536697</v>
       </c>
       <c r="R38" t="n">
-        <v>7204779</v>
+        <v>7204666</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4880,7 +4885,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4890,7 +4895,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4901,11 +4906,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4922,10 +4922,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934207</v>
+        <v>119934066</v>
       </c>
       <c r="B39" t="n">
-        <v>90558</v>
+        <v>90509</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4938,21 +4938,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4962,10 +4962,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536704</v>
+        <v>536771</v>
       </c>
       <c r="R39" t="n">
-        <v>7204580</v>
+        <v>7204791</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5018,6 +5018,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5034,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934221</v>
+        <v>119934207</v>
       </c>
       <c r="B40" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5050,21 +5065,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5074,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536697</v>
+        <v>536704</v>
       </c>
       <c r="R40" t="n">
-        <v>7204666</v>
+        <v>7204580</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5109,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5119,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5146,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934066</v>
+        <v>119934078</v>
       </c>
       <c r="B41" t="n">
-        <v>90509</v>
+        <v>79608</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5162,21 +5177,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>112</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5186,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536771</v>
+        <v>536606</v>
       </c>
       <c r="R41" t="n">
-        <v>7204791</v>
+        <v>7204748</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5221,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5231,7 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5242,21 +5257,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934009</v>
+        <v>119934015</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536410</v>
+        <v>536441</v>
       </c>
       <c r="R5" t="n">
-        <v>7204341</v>
+        <v>7204337</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934015</v>
+        <v>119934009</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536441</v>
+        <v>536410</v>
       </c>
       <c r="R6" t="n">
-        <v>7204337</v>
+        <v>7204341</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -4810,10 +4810,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934221</v>
+        <v>119934066</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>90509</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536697</v>
+        <v>536771</v>
       </c>
       <c r="R38" t="n">
-        <v>7204666</v>
+        <v>7204791</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4906,6 +4906,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4922,10 +4937,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934066</v>
+        <v>119934207</v>
       </c>
       <c r="B39" t="n">
-        <v>90509</v>
+        <v>90558</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4938,21 +4953,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4962,10 +4977,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536771</v>
+        <v>536704</v>
       </c>
       <c r="R39" t="n">
-        <v>7204791</v>
+        <v>7204580</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4997,7 +5012,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5007,7 +5022,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5018,21 +5033,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5049,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934207</v>
+        <v>119934078</v>
       </c>
       <c r="B40" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5065,21 +5065,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536704</v>
+        <v>536606</v>
       </c>
       <c r="R40" t="n">
-        <v>7204580</v>
+        <v>7204748</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934078</v>
+        <v>119934221</v>
       </c>
       <c r="B41" t="n">
-        <v>79608</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536606</v>
+        <v>536697</v>
       </c>
       <c r="R41" t="n">
-        <v>7204748</v>
+        <v>7204666</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934015</v>
+        <v>119934009</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536441</v>
+        <v>536410</v>
       </c>
       <c r="R5" t="n">
-        <v>7204337</v>
+        <v>7204341</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934009</v>
+        <v>119934015</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536410</v>
+        <v>536441</v>
       </c>
       <c r="R6" t="n">
-        <v>7204341</v>
+        <v>7204337</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3428,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934217</v>
+        <v>119934064</v>
       </c>
       <c r="B26" t="n">
-        <v>90576</v>
+        <v>97074</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,25 +3440,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>220250</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536771</v>
+        <v>536851</v>
       </c>
       <c r="R26" t="n">
-        <v>7204791</v>
+        <v>7204845</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3524,21 +3524,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3555,10 +3540,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934080</v>
+        <v>119934217</v>
       </c>
       <c r="B27" t="n">
-        <v>79608</v>
+        <v>90576</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3571,21 +3556,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3595,10 +3580,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536865</v>
+        <v>536771</v>
       </c>
       <c r="R27" t="n">
-        <v>7204832</v>
+        <v>7204791</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3630,7 +3615,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3640,7 +3625,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,6 +3636,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3667,10 +3667,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934064</v>
+        <v>119934080</v>
       </c>
       <c r="B28" t="n">
-        <v>97074</v>
+        <v>79608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3679,25 +3679,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220250</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536851</v>
+        <v>536865</v>
       </c>
       <c r="R28" t="n">
-        <v>7204845</v>
+        <v>7204832</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4358,10 +4358,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934208</v>
+        <v>119934210</v>
       </c>
       <c r="B34" t="n">
-        <v>90558</v>
+        <v>74622</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4370,25 +4370,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536690</v>
+        <v>536837</v>
       </c>
       <c r="R34" t="n">
-        <v>7204670</v>
+        <v>7204821</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934210</v>
+        <v>119934208</v>
       </c>
       <c r="B35" t="n">
-        <v>74622</v>
+        <v>90558</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4482,25 +4482,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536837</v>
+        <v>536690</v>
       </c>
       <c r="R35" t="n">
-        <v>7204821</v>
+        <v>7204670</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4810,10 +4810,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934066</v>
+        <v>119934221</v>
       </c>
       <c r="B38" t="n">
-        <v>90509</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536771</v>
+        <v>536697</v>
       </c>
       <c r="R38" t="n">
-        <v>7204791</v>
+        <v>7204666</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4906,21 +4906,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4937,10 +4922,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934207</v>
+        <v>119934066</v>
       </c>
       <c r="B39" t="n">
-        <v>90558</v>
+        <v>90509</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4953,21 +4938,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4977,10 +4962,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536704</v>
+        <v>536771</v>
       </c>
       <c r="R39" t="n">
-        <v>7204580</v>
+        <v>7204791</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5012,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5022,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5033,6 +5018,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5049,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934078</v>
+        <v>119934207</v>
       </c>
       <c r="B40" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5065,21 +5065,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536606</v>
+        <v>536704</v>
       </c>
       <c r="R40" t="n">
-        <v>7204748</v>
+        <v>7204580</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934221</v>
+        <v>119934078</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>79608</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536697</v>
+        <v>536606</v>
       </c>
       <c r="R41" t="n">
-        <v>7204666</v>
+        <v>7204748</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934009</v>
+        <v>119934015</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536410</v>
+        <v>536441</v>
       </c>
       <c r="R5" t="n">
-        <v>7204341</v>
+        <v>7204337</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934015</v>
+        <v>119934009</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536441</v>
+        <v>536410</v>
       </c>
       <c r="R6" t="n">
-        <v>7204337</v>
+        <v>7204341</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934016</v>
+        <v>119934251</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,39 +1617,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536575</v>
+        <v>536625</v>
       </c>
       <c r="R10" t="n">
-        <v>7204458</v>
+        <v>7204790</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,6 +1697,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934251</v>
+        <v>119934016</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,34 +1744,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536625</v>
+        <v>536575</v>
       </c>
       <c r="R11" t="n">
-        <v>7204790</v>
+        <v>7204458</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1793,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,21 +1829,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -3428,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934064</v>
+        <v>119934217</v>
       </c>
       <c r="B26" t="n">
-        <v>97074</v>
+        <v>90576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,25 +3440,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220250</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536851</v>
+        <v>536771</v>
       </c>
       <c r="R26" t="n">
-        <v>7204845</v>
+        <v>7204791</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3524,6 +3524,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3540,10 +3555,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934217</v>
+        <v>119934080</v>
       </c>
       <c r="B27" t="n">
-        <v>90576</v>
+        <v>79608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,21 +3571,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3580,10 +3595,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536771</v>
+        <v>536865</v>
       </c>
       <c r="R27" t="n">
-        <v>7204791</v>
+        <v>7204832</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3615,7 +3630,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3625,7 +3640,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,21 +3651,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3667,10 +3667,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934080</v>
+        <v>119934064</v>
       </c>
       <c r="B28" t="n">
-        <v>79608</v>
+        <v>97074</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3679,25 +3679,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>220250</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536865</v>
+        <v>536851</v>
       </c>
       <c r="R28" t="n">
-        <v>7204832</v>
+        <v>7204845</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4358,10 +4358,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934210</v>
+        <v>119934208</v>
       </c>
       <c r="B34" t="n">
-        <v>74622</v>
+        <v>90558</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4370,25 +4370,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536837</v>
+        <v>536690</v>
       </c>
       <c r="R34" t="n">
-        <v>7204821</v>
+        <v>7204670</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934208</v>
+        <v>119934210</v>
       </c>
       <c r="B35" t="n">
-        <v>90558</v>
+        <v>74622</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4482,25 +4482,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536690</v>
+        <v>536837</v>
       </c>
       <c r="R35" t="n">
-        <v>7204670</v>
+        <v>7204821</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934015</v>
+        <v>119934009</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536441</v>
+        <v>536410</v>
       </c>
       <c r="R5" t="n">
-        <v>7204337</v>
+        <v>7204341</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934009</v>
+        <v>119934015</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536410</v>
+        <v>536441</v>
       </c>
       <c r="R6" t="n">
-        <v>7204341</v>
+        <v>7204337</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934251</v>
+        <v>119934016</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,34 +1617,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536625</v>
+        <v>536575</v>
       </c>
       <c r="R10" t="n">
-        <v>7204790</v>
+        <v>7204458</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,21 +1702,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1728,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934016</v>
+        <v>119934251</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,39 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536575</v>
+        <v>536625</v>
       </c>
       <c r="R11" t="n">
-        <v>7204458</v>
+        <v>7204790</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,6 +1814,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934009</v>
+        <v>119934015</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536410</v>
+        <v>536441</v>
       </c>
       <c r="R5" t="n">
-        <v>7204341</v>
+        <v>7204337</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934015</v>
+        <v>119934009</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536441</v>
+        <v>536410</v>
       </c>
       <c r="R6" t="n">
-        <v>7204337</v>
+        <v>7204341</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934016</v>
+        <v>119934251</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,39 +1617,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536575</v>
+        <v>536625</v>
       </c>
       <c r="R10" t="n">
-        <v>7204458</v>
+        <v>7204790</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,6 +1697,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934251</v>
+        <v>119934016</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,34 +1744,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536625</v>
+        <v>536575</v>
       </c>
       <c r="R11" t="n">
-        <v>7204790</v>
+        <v>7204458</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1793,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,21 +1829,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -4358,10 +4358,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934208</v>
+        <v>119934210</v>
       </c>
       <c r="B34" t="n">
-        <v>90558</v>
+        <v>74622</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4370,25 +4370,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536690</v>
+        <v>536837</v>
       </c>
       <c r="R34" t="n">
-        <v>7204670</v>
+        <v>7204821</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934210</v>
+        <v>119934208</v>
       </c>
       <c r="B35" t="n">
-        <v>74622</v>
+        <v>90558</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4482,25 +4482,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536837</v>
+        <v>536690</v>
       </c>
       <c r="R35" t="n">
-        <v>7204821</v>
+        <v>7204670</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934203</v>
+        <v>119934015</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536405</v>
+        <v>536441</v>
       </c>
       <c r="R2" t="n">
-        <v>7204335</v>
+        <v>7204337</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934014</v>
+        <v>119934203</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>78624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536418</v>
+        <v>536405</v>
       </c>
       <c r="R3" t="n">
-        <v>7204363</v>
+        <v>7204335</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
         <v>119934245</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934015</v>
+        <v>119934014</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536441</v>
+        <v>536418</v>
       </c>
       <c r="R5" t="n">
-        <v>7204337</v>
+        <v>7204363</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
         <v>119934009</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934004</v>
+        <v>119934249</v>
       </c>
       <c r="B7" t="n">
-        <v>89633</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536620</v>
+        <v>536683</v>
       </c>
       <c r="R7" t="n">
-        <v>7204779</v>
+        <v>7204683</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,11 +1341,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119933991</v>
+        <v>119934065</v>
       </c>
       <c r="B8" t="n">
-        <v>86057</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3294</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536861</v>
+        <v>536683</v>
       </c>
       <c r="R8" t="n">
-        <v>7204835</v>
+        <v>7204683</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934218</v>
+        <v>119934215</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>90594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536789</v>
+        <v>536591</v>
       </c>
       <c r="R9" t="n">
-        <v>7204793</v>
+        <v>7204751</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,21 +1565,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1601,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934251</v>
+        <v>119934216</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>90594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536625</v>
+        <v>536769</v>
       </c>
       <c r="R10" t="n">
-        <v>7204790</v>
+        <v>7204825</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934016</v>
+        <v>119934208</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,39 +1724,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536575</v>
+        <v>536690</v>
       </c>
       <c r="R11" t="n">
-        <v>7204458</v>
+        <v>7204670</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934079</v>
+        <v>119934218</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
+        <v>90594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536847</v>
+        <v>536789</v>
       </c>
       <c r="R12" t="n">
-        <v>7204825</v>
+        <v>7204793</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1920,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,6 +1916,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1957,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934249</v>
+        <v>119934030</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>56532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,38 +1959,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536683</v>
+        <v>536532</v>
       </c>
       <c r="R13" t="n">
-        <v>7204683</v>
+        <v>7204362</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2032,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934247</v>
+        <v>119934064</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>97097</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,25 +2075,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220250</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2109,10 +2103,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536691</v>
+        <v>536851</v>
       </c>
       <c r="R14" t="n">
-        <v>7204650</v>
+        <v>7204845</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2144,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2148,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,10 +2175,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934250</v>
+        <v>119934184</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>94334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,25 +2187,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2221,10 +2215,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536603</v>
+        <v>536806</v>
       </c>
       <c r="R15" t="n">
-        <v>7204748</v>
+        <v>7204783</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2256,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934246</v>
+        <v>119934114</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>94346</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,25 +2299,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2333,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536532</v>
+        <v>536852</v>
       </c>
       <c r="R16" t="n">
-        <v>7204362</v>
+        <v>7204836</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2368,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934194</v>
+        <v>119934247</v>
       </c>
       <c r="B17" t="n">
-        <v>79643</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,25 +2411,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2445,10 +2439,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536627</v>
+        <v>536691</v>
       </c>
       <c r="R17" t="n">
-        <v>7204789</v>
+        <v>7204650</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2480,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2490,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934065</v>
+        <v>119934081</v>
       </c>
       <c r="B18" t="n">
-        <v>90509</v>
+        <v>79624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2557,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536683</v>
+        <v>536882</v>
       </c>
       <c r="R18" t="n">
-        <v>7204683</v>
+        <v>7204819</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2592,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2602,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934137</v>
+        <v>119934217</v>
       </c>
       <c r="B19" t="n">
-        <v>74643</v>
+        <v>90594</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2645,21 +2639,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2669,10 +2663,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536837</v>
+        <v>536771</v>
       </c>
       <c r="R19" t="n">
-        <v>7204821</v>
+        <v>7204791</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2704,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2714,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,6 +2719,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2741,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934253</v>
+        <v>119934194</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>79659</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2753,25 +2762,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2781,10 +2790,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536884</v>
+        <v>536627</v>
       </c>
       <c r="R20" t="n">
-        <v>7204818</v>
+        <v>7204789</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2816,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2826,7 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934052</v>
+        <v>119934250</v>
       </c>
       <c r="B21" t="n">
-        <v>91339</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,25 +2874,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>918</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,10 +2902,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536807</v>
+        <v>536603</v>
       </c>
       <c r="R21" t="n">
-        <v>7204778</v>
+        <v>7204748</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2928,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2938,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,21 +2958,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2980,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934215</v>
+        <v>119934214</v>
       </c>
       <c r="B22" t="n">
-        <v>90576</v>
+        <v>90594</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3020,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536591</v>
+        <v>536641</v>
       </c>
       <c r="R22" t="n">
-        <v>7204751</v>
+        <v>7204731</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3055,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3065,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934062</v>
+        <v>119934248</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3104,25 +3098,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3132,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536865</v>
+        <v>536694</v>
       </c>
       <c r="R23" t="n">
-        <v>7204832</v>
+        <v>7204667</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3167,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3177,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3204,10 +3198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934252</v>
+        <v>119934079</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>79624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3220,21 +3214,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,10 +3238,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536859</v>
+        <v>536847</v>
       </c>
       <c r="R24" t="n">
-        <v>7204833</v>
+        <v>7204825</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3279,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,10 +3310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934081</v>
+        <v>119934066</v>
       </c>
       <c r="B25" t="n">
-        <v>79608</v>
+        <v>90527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,21 +3326,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3356,10 +3350,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536882</v>
+        <v>536771</v>
       </c>
       <c r="R25" t="n">
-        <v>7204819</v>
+        <v>7204791</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3391,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,6 +3406,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3428,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934217</v>
+        <v>119934252</v>
       </c>
       <c r="B26" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,21 +3453,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3468,10 +3477,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536771</v>
+        <v>536859</v>
       </c>
       <c r="R26" t="n">
-        <v>7204791</v>
+        <v>7204833</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3503,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3513,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3524,21 +3533,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3555,10 +3549,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934080</v>
+        <v>119934004</v>
       </c>
       <c r="B27" t="n">
-        <v>79608</v>
+        <v>89650</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3571,21 +3565,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3595,10 +3589,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536865</v>
+        <v>536620</v>
       </c>
       <c r="R27" t="n">
-        <v>7204832</v>
+        <v>7204779</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3630,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3640,7 +3634,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,6 +3645,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3667,10 +3666,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934064</v>
+        <v>119934246</v>
       </c>
       <c r="B28" t="n">
-        <v>97074</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3679,25 +3678,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220250</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3707,10 +3706,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536851</v>
+        <v>536532</v>
       </c>
       <c r="R28" t="n">
-        <v>7204845</v>
+        <v>7204362</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3742,7 +3741,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3752,7 +3751,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3779,10 +3778,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934248</v>
+        <v>119934137</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>74659</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3795,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3819,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536694</v>
+        <v>536837</v>
       </c>
       <c r="R29" t="n">
-        <v>7204667</v>
+        <v>7204821</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3854,7 +3853,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3864,7 +3863,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3891,10 +3890,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934184</v>
+        <v>119934080</v>
       </c>
       <c r="B30" t="n">
-        <v>94311</v>
+        <v>79624</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3903,25 +3902,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3931,10 +3930,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536806</v>
+        <v>536865</v>
       </c>
       <c r="R30" t="n">
-        <v>7204783</v>
+        <v>7204832</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3966,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3976,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4003,10 +4002,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934114</v>
+        <v>119934016</v>
       </c>
       <c r="B31" t="n">
-        <v>94323</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4015,38 +4014,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536852</v>
+        <v>536575</v>
       </c>
       <c r="R31" t="n">
-        <v>7204836</v>
+        <v>7204458</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4078,7 +4082,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4088,7 +4092,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,10 +4119,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934216</v>
+        <v>119934052</v>
       </c>
       <c r="B32" t="n">
-        <v>90576</v>
+        <v>91357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4127,25 +4131,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>918</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4155,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536769</v>
+        <v>536807</v>
       </c>
       <c r="R32" t="n">
-        <v>7204825</v>
+        <v>7204778</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4190,7 +4194,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4200,7 +4204,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4245,7 +4249,7 @@
         <v>119934041</v>
       </c>
       <c r="B33" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4358,10 +4362,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934210</v>
+        <v>119934251</v>
       </c>
       <c r="B34" t="n">
-        <v>74622</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4370,25 +4374,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4398,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536837</v>
+        <v>536625</v>
       </c>
       <c r="R34" t="n">
-        <v>7204821</v>
+        <v>7204790</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4433,7 +4437,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4443,7 +4447,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4454,6 +4458,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4470,10 +4489,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934208</v>
+        <v>119934210</v>
       </c>
       <c r="B35" t="n">
-        <v>90558</v>
+        <v>74638</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4482,25 +4501,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4510,10 +4529,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536690</v>
+        <v>536837</v>
       </c>
       <c r="R35" t="n">
-        <v>7204670</v>
+        <v>7204821</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4545,7 +4564,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4555,7 +4574,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4582,10 +4601,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934214</v>
+        <v>119933991</v>
       </c>
       <c r="B36" t="n">
-        <v>90576</v>
+        <v>86074</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4594,25 +4613,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>3294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4622,10 +4641,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536641</v>
+        <v>536861</v>
       </c>
       <c r="R36" t="n">
-        <v>7204731</v>
+        <v>7204835</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4657,7 +4676,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4667,7 +4686,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4694,10 +4713,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934030</v>
+        <v>119934221</v>
       </c>
       <c r="B37" t="n">
-        <v>56522</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4706,42 +4725,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536532</v>
+        <v>536697</v>
       </c>
       <c r="R37" t="n">
-        <v>7204362</v>
+        <v>7204666</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4773,7 +4788,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4783,7 +4798,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4810,10 +4825,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934221</v>
+        <v>119934207</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4826,21 +4841,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4850,10 +4865,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536697</v>
+        <v>536704</v>
       </c>
       <c r="R38" t="n">
-        <v>7204666</v>
+        <v>7204580</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4885,7 +4900,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4895,7 +4910,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4922,10 +4937,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934066</v>
+        <v>119934062</v>
       </c>
       <c r="B39" t="n">
-        <v>90509</v>
+        <v>79652</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4934,25 +4949,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4962,10 +4977,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536771</v>
+        <v>536865</v>
       </c>
       <c r="R39" t="n">
-        <v>7204791</v>
+        <v>7204832</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4997,7 +5012,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5007,7 +5022,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5018,21 +5033,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5049,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934207</v>
+        <v>119934078</v>
       </c>
       <c r="B40" t="n">
-        <v>90558</v>
+        <v>79624</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5065,21 +5065,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536704</v>
+        <v>536606</v>
       </c>
       <c r="R40" t="n">
-        <v>7204580</v>
+        <v>7204748</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934078</v>
+        <v>119934253</v>
       </c>
       <c r="B41" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536606</v>
+        <v>536884</v>
       </c>
       <c r="R41" t="n">
-        <v>7204748</v>
+        <v>7204818</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934015</v>
+        <v>119934203</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536441</v>
+        <v>536405</v>
       </c>
       <c r="R2" t="n">
-        <v>7204337</v>
+        <v>7204335</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934203</v>
+        <v>119934015</v>
       </c>
       <c r="B3" t="n">
-        <v>78624</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536405</v>
+        <v>536441</v>
       </c>
       <c r="R3" t="n">
-        <v>7204335</v>
+        <v>7204337</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934081</v>
+        <v>119934217</v>
       </c>
       <c r="B18" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536882</v>
+        <v>536771</v>
       </c>
       <c r="R18" t="n">
-        <v>7204819</v>
+        <v>7204791</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,6 +2607,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2623,10 +2638,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934217</v>
+        <v>119934081</v>
       </c>
       <c r="B19" t="n">
-        <v>90594</v>
+        <v>79624</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2654,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,10 +2678,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536771</v>
+        <v>536882</v>
       </c>
       <c r="R19" t="n">
-        <v>7204791</v>
+        <v>7204819</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,21 +2734,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3437,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934252</v>
+        <v>119934004</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3453,21 +3453,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536859</v>
+        <v>536620</v>
       </c>
       <c r="R26" t="n">
-        <v>7204833</v>
+        <v>7204779</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,6 +3533,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3549,10 +3554,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934004</v>
+        <v>119934252</v>
       </c>
       <c r="B27" t="n">
-        <v>89650</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,21 +3570,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3589,10 +3594,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536620</v>
+        <v>536859</v>
       </c>
       <c r="R27" t="n">
-        <v>7204779</v>
+        <v>7204833</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3624,7 +3629,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3634,7 +3639,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,11 +3650,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4246,10 +4246,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934041</v>
+        <v>119934251</v>
       </c>
       <c r="B33" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4262,38 +4262,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536542</v>
+        <v>536625</v>
       </c>
       <c r="R33" t="n">
-        <v>7204366</v>
+        <v>7204790</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4325,7 +4321,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4335,7 +4331,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4346,6 +4342,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4362,10 +4373,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934251</v>
+        <v>119934210</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>74638</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4374,25 +4385,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4402,10 +4413,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536625</v>
+        <v>536837</v>
       </c>
       <c r="R34" t="n">
-        <v>7204790</v>
+        <v>7204821</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4437,7 +4448,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4447,7 +4458,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4458,21 +4469,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4489,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934210</v>
+        <v>119934041</v>
       </c>
       <c r="B35" t="n">
-        <v>74638</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4501,38 +4497,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536837</v>
+        <v>536542</v>
       </c>
       <c r="R35" t="n">
-        <v>7204821</v>
+        <v>7204366</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934203</v>
+        <v>119934009</v>
       </c>
       <c r="B2" t="n">
-        <v>78624</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536405</v>
+        <v>536410</v>
       </c>
       <c r="R2" t="n">
-        <v>7204335</v>
+        <v>7204341</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934009</v>
+        <v>119934203</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>78624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536410</v>
+        <v>536405</v>
       </c>
       <c r="R6" t="n">
-        <v>7204341</v>
+        <v>7204335</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934249</v>
+        <v>119934215</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536683</v>
+        <v>536591</v>
       </c>
       <c r="R7" t="n">
-        <v>7204683</v>
+        <v>7204751</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934065</v>
+        <v>119934208</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>90576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536683</v>
+        <v>536690</v>
       </c>
       <c r="R8" t="n">
-        <v>7204683</v>
+        <v>7204670</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934215</v>
+        <v>119934248</v>
       </c>
       <c r="B9" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536591</v>
+        <v>536694</v>
       </c>
       <c r="R9" t="n">
-        <v>7204751</v>
+        <v>7204667</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934216</v>
+        <v>119934137</v>
       </c>
       <c r="B10" t="n">
-        <v>90594</v>
+        <v>74659</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536769</v>
+        <v>536837</v>
       </c>
       <c r="R10" t="n">
-        <v>7204825</v>
+        <v>7204821</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,21 +1677,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1708,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934208</v>
+        <v>119934052</v>
       </c>
       <c r="B11" t="n">
-        <v>90576</v>
+        <v>91357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536690</v>
+        <v>536807</v>
       </c>
       <c r="R11" t="n">
-        <v>7204670</v>
+        <v>7204778</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,6 +1789,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934218</v>
+        <v>119934251</v>
       </c>
       <c r="B12" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536789</v>
+        <v>536625</v>
       </c>
       <c r="R12" t="n">
-        <v>7204793</v>
+        <v>7204790</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934030</v>
+        <v>119934252</v>
       </c>
       <c r="B13" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,42 +1959,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536532</v>
+        <v>536859</v>
       </c>
       <c r="R13" t="n">
-        <v>7204362</v>
+        <v>7204833</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2026,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934064</v>
+        <v>119934081</v>
       </c>
       <c r="B14" t="n">
-        <v>97097</v>
+        <v>79624</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,25 +2071,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220250</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2103,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536851</v>
+        <v>536882</v>
       </c>
       <c r="R14" t="n">
-        <v>7204845</v>
+        <v>7204819</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2138,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934184</v>
+        <v>119934080</v>
       </c>
       <c r="B15" t="n">
-        <v>94334</v>
+        <v>79624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,25 +2183,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2215,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536806</v>
+        <v>536865</v>
       </c>
       <c r="R15" t="n">
-        <v>7204783</v>
+        <v>7204832</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2250,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2283,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934114</v>
+        <v>119933991</v>
       </c>
       <c r="B16" t="n">
-        <v>94346</v>
+        <v>86074</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,21 +2299,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2813</v>
+        <v>3294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2327,10 +2323,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536852</v>
+        <v>536861</v>
       </c>
       <c r="R16" t="n">
-        <v>7204836</v>
+        <v>7204835</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2368,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934247</v>
+        <v>119934041</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,34 +2411,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536691</v>
+        <v>536542</v>
       </c>
       <c r="R17" t="n">
-        <v>7204650</v>
+        <v>7204366</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934217</v>
+        <v>119934065</v>
       </c>
       <c r="B18" t="n">
-        <v>90594</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536771</v>
+        <v>536683</v>
       </c>
       <c r="R18" t="n">
-        <v>7204791</v>
+        <v>7204683</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,21 +2607,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2638,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934081</v>
+        <v>119934217</v>
       </c>
       <c r="B19" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,21 +2639,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2678,10 +2663,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536882</v>
+        <v>536771</v>
       </c>
       <c r="R19" t="n">
-        <v>7204819</v>
+        <v>7204791</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2713,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,6 +2719,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934194</v>
+        <v>119934062</v>
       </c>
       <c r="B20" t="n">
-        <v>79659</v>
+        <v>79652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,21 +2766,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536627</v>
+        <v>536865</v>
       </c>
       <c r="R20" t="n">
-        <v>7204789</v>
+        <v>7204832</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934250</v>
+        <v>119934030</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,38 +2874,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536603</v>
+        <v>536532</v>
       </c>
       <c r="R21" t="n">
-        <v>7204748</v>
+        <v>7204362</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2937,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,7 +2978,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934214</v>
+        <v>119934216</v>
       </c>
       <c r="B22" t="n">
         <v>90594</v>
@@ -3014,10 +3018,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536641</v>
+        <v>536769</v>
       </c>
       <c r="R22" t="n">
-        <v>7204731</v>
+        <v>7204825</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3049,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,6 +3074,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3086,7 +3105,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934248</v>
+        <v>119934250</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -3126,10 +3145,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536694</v>
+        <v>536603</v>
       </c>
       <c r="R23" t="n">
-        <v>7204667</v>
+        <v>7204748</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3161,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,10 +3217,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934079</v>
+        <v>119934246</v>
       </c>
       <c r="B24" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3214,21 +3233,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3238,10 +3257,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536847</v>
+        <v>536532</v>
       </c>
       <c r="R24" t="n">
-        <v>7204825</v>
+        <v>7204362</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3273,7 +3292,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3302,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,10 +3329,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934066</v>
+        <v>119934184</v>
       </c>
       <c r="B25" t="n">
-        <v>90527</v>
+        <v>94334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3322,25 +3341,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3350,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536771</v>
+        <v>536806</v>
       </c>
       <c r="R25" t="n">
-        <v>7204791</v>
+        <v>7204783</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3385,7 +3404,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3414,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3406,21 +3425,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3437,10 +3441,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934004</v>
+        <v>119934210</v>
       </c>
       <c r="B26" t="n">
-        <v>89650</v>
+        <v>74638</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3449,25 +3453,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3477,10 +3481,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536620</v>
+        <v>536837</v>
       </c>
       <c r="R26" t="n">
-        <v>7204779</v>
+        <v>7204821</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,7 +3526,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,11 +3537,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3554,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934252</v>
+        <v>119934004</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3570,21 +3569,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3594,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536859</v>
+        <v>536620</v>
       </c>
       <c r="R27" t="n">
-        <v>7204833</v>
+        <v>7204779</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3629,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3639,7 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,6 +3649,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3666,10 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934246</v>
+        <v>119934079</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3682,21 +3686,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3706,10 +3710,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536532</v>
+        <v>536847</v>
       </c>
       <c r="R28" t="n">
-        <v>7204362</v>
+        <v>7204825</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3741,7 +3745,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3751,7 +3755,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3778,10 +3782,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934137</v>
+        <v>119934218</v>
       </c>
       <c r="B29" t="n">
-        <v>74659</v>
+        <v>90594</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3794,21 +3798,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3822,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536837</v>
+        <v>536789</v>
       </c>
       <c r="R29" t="n">
-        <v>7204821</v>
+        <v>7204793</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3853,7 +3857,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3863,7 +3867,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3874,6 +3878,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3890,10 +3909,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934080</v>
+        <v>119934253</v>
       </c>
       <c r="B30" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3906,21 +3925,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3930,10 +3949,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536865</v>
+        <v>536884</v>
       </c>
       <c r="R30" t="n">
-        <v>7204832</v>
+        <v>7204818</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3965,7 +3984,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3994,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4002,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934016</v>
+        <v>119934194</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>79659</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4014,43 +4033,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536575</v>
+        <v>536627</v>
       </c>
       <c r="R31" t="n">
-        <v>7204458</v>
+        <v>7204789</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4082,7 +4096,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4092,7 +4106,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4119,10 +4133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934052</v>
+        <v>119934064</v>
       </c>
       <c r="B32" t="n">
-        <v>91357</v>
+        <v>97097</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4131,25 +4145,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>918</v>
+        <v>220250</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4159,10 +4173,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536807</v>
+        <v>536851</v>
       </c>
       <c r="R32" t="n">
-        <v>7204778</v>
+        <v>7204845</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4194,7 +4208,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4204,7 +4218,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4215,21 +4229,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4246,10 +4245,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934251</v>
+        <v>119934214</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4262,21 +4261,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4286,10 +4285,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536625</v>
+        <v>536641</v>
       </c>
       <c r="R33" t="n">
-        <v>7204790</v>
+        <v>7204731</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4321,7 +4320,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4331,7 +4330,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4342,21 +4341,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4373,10 +4357,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934210</v>
+        <v>119934016</v>
       </c>
       <c r="B34" t="n">
-        <v>74638</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4385,38 +4369,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536837</v>
+        <v>536575</v>
       </c>
       <c r="R34" t="n">
-        <v>7204821</v>
+        <v>7204458</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4448,7 +4437,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4458,7 +4447,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4485,10 +4474,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934041</v>
+        <v>119934249</v>
       </c>
       <c r="B35" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4501,38 +4490,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536542</v>
+        <v>536683</v>
       </c>
       <c r="R35" t="n">
-        <v>7204366</v>
+        <v>7204683</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4564,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4574,7 +4559,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4601,10 +4586,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119933991</v>
+        <v>119934221</v>
       </c>
       <c r="B36" t="n">
-        <v>86074</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4613,25 +4598,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3294</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4641,10 +4626,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536861</v>
+        <v>536697</v>
       </c>
       <c r="R36" t="n">
-        <v>7204835</v>
+        <v>7204666</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4676,7 +4661,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4686,7 +4671,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4713,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934221</v>
+        <v>119934078</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4729,21 +4714,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4753,10 +4738,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536697</v>
+        <v>536606</v>
       </c>
       <c r="R37" t="n">
-        <v>7204666</v>
+        <v>7204748</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4788,7 +4773,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4798,7 +4783,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4937,10 +4922,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934062</v>
+        <v>119934247</v>
       </c>
       <c r="B39" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4949,25 +4934,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4977,10 +4962,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536865</v>
+        <v>536691</v>
       </c>
       <c r="R39" t="n">
-        <v>7204832</v>
+        <v>7204650</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5012,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5022,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5049,10 +5034,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934078</v>
+        <v>119934114</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>94346</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5061,25 +5046,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>2813</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5074,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536606</v>
+        <v>536852</v>
       </c>
       <c r="R40" t="n">
-        <v>7204748</v>
+        <v>7204836</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5124,7 +5109,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5134,7 +5119,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,10 +5146,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934253</v>
+        <v>119934066</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>90527</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5177,21 +5162,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5201,10 +5186,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536884</v>
+        <v>536771</v>
       </c>
       <c r="R41" t="n">
-        <v>7204818</v>
+        <v>7204791</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5236,7 +5221,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5246,7 +5231,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5257,6 +5242,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -2395,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934041</v>
+        <v>119934065</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>90527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,38 +2411,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536542</v>
+        <v>536683</v>
       </c>
       <c r="R17" t="n">
-        <v>7204366</v>
+        <v>7204683</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2507,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934065</v>
+        <v>119934041</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,34 +2523,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536683</v>
+        <v>536542</v>
       </c>
       <c r="R18" t="n">
-        <v>7204683</v>
+        <v>7204366</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934062</v>
+        <v>119934030</v>
       </c>
       <c r="B20" t="n">
-        <v>79652</v>
+        <v>56532</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,34 +2766,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536865</v>
+        <v>536532</v>
       </c>
       <c r="R20" t="n">
-        <v>7204832</v>
+        <v>7204362</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2825,7 +2829,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934030</v>
+        <v>119934062</v>
       </c>
       <c r="B21" t="n">
-        <v>56532</v>
+        <v>79652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,38 +2882,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536532</v>
+        <v>536865</v>
       </c>
       <c r="R21" t="n">
-        <v>7204362</v>
+        <v>7204832</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934216</v>
+        <v>119934250</v>
       </c>
       <c r="B22" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,21 +2994,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536769</v>
+        <v>536603</v>
       </c>
       <c r="R22" t="n">
-        <v>7204825</v>
+        <v>7204748</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,21 +3074,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3105,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934250</v>
+        <v>119934216</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3121,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3145,10 +3130,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536603</v>
+        <v>536769</v>
       </c>
       <c r="R23" t="n">
-        <v>7204748</v>
+        <v>7204825</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3180,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,6 +3186,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -4810,10 +4810,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934207</v>
+        <v>119934114</v>
       </c>
       <c r="B38" t="n">
-        <v>90576</v>
+        <v>94346</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4822,25 +4822,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>2813</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536704</v>
+        <v>536852</v>
       </c>
       <c r="R38" t="n">
-        <v>7204580</v>
+        <v>7204836</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4922,10 +4922,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934247</v>
+        <v>119934207</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4938,21 +4938,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4962,10 +4962,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536691</v>
+        <v>536704</v>
       </c>
       <c r="R39" t="n">
-        <v>7204650</v>
+        <v>7204580</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5034,10 +5034,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934114</v>
+        <v>119934247</v>
       </c>
       <c r="B40" t="n">
-        <v>94346</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5046,25 +5046,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536852</v>
+        <v>536691</v>
       </c>
       <c r="R40" t="n">
-        <v>7204836</v>
+        <v>7204650</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934009</v>
+        <v>119934245</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536410</v>
+        <v>536407</v>
       </c>
       <c r="R2" t="n">
-        <v>7204341</v>
+        <v>7204331</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934015</v>
+        <v>119934203</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536441</v>
+        <v>536405</v>
       </c>
       <c r="R3" t="n">
-        <v>7204337</v>
+        <v>7204335</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934245</v>
+        <v>119934014</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536407</v>
+        <v>536418</v>
       </c>
       <c r="R4" t="n">
-        <v>7204331</v>
+        <v>7204363</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934014</v>
+        <v>119934009</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536418</v>
+        <v>536410</v>
       </c>
       <c r="R5" t="n">
-        <v>7204363</v>
+        <v>7204341</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934203</v>
+        <v>119934015</v>
       </c>
       <c r="B6" t="n">
-        <v>78624</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536405</v>
+        <v>536441</v>
       </c>
       <c r="R6" t="n">
-        <v>7204335</v>
+        <v>7204337</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934215</v>
+        <v>119934066</v>
       </c>
       <c r="B7" t="n">
-        <v>90594</v>
+        <v>90527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536591</v>
+        <v>536771</v>
       </c>
       <c r="R7" t="n">
-        <v>7204751</v>
+        <v>7204791</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,6 +1341,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934208</v>
+        <v>119934079</v>
       </c>
       <c r="B8" t="n">
-        <v>90576</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536690</v>
+        <v>536847</v>
       </c>
       <c r="R8" t="n">
-        <v>7204670</v>
+        <v>7204825</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934248</v>
+        <v>119934250</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1509,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536694</v>
+        <v>536603</v>
       </c>
       <c r="R9" t="n">
-        <v>7204667</v>
+        <v>7204748</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934137</v>
+        <v>119934062</v>
       </c>
       <c r="B10" t="n">
-        <v>74659</v>
+        <v>79652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536837</v>
+        <v>536865</v>
       </c>
       <c r="R10" t="n">
-        <v>7204821</v>
+        <v>7204832</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934052</v>
+        <v>119934030</v>
       </c>
       <c r="B11" t="n">
-        <v>91357</v>
+        <v>56532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,38 +1720,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>918</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536807</v>
+        <v>536532</v>
       </c>
       <c r="R11" t="n">
-        <v>7204778</v>
+        <v>7204362</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,21 +1808,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934251</v>
+        <v>119934184</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,25 +1836,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536625</v>
+        <v>536806</v>
       </c>
       <c r="R12" t="n">
-        <v>7204790</v>
+        <v>7204783</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,21 +1920,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1947,7 +1936,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934252</v>
+        <v>119934249</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1987,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536859</v>
+        <v>536683</v>
       </c>
       <c r="R13" t="n">
-        <v>7204833</v>
+        <v>7204683</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2022,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934081</v>
+        <v>119934251</v>
       </c>
       <c r="B14" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,21 +2064,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,10 +2088,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536882</v>
+        <v>536625</v>
       </c>
       <c r="R14" t="n">
-        <v>7204819</v>
+        <v>7204790</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2134,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2133,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,6 +2144,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2171,10 +2175,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934080</v>
+        <v>119934253</v>
       </c>
       <c r="B15" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,21 +2191,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2211,10 +2215,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536865</v>
+        <v>536884</v>
       </c>
       <c r="R15" t="n">
-        <v>7204832</v>
+        <v>7204818</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2246,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119933991</v>
+        <v>119934207</v>
       </c>
       <c r="B16" t="n">
-        <v>86074</v>
+        <v>90576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,25 +2299,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3294</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2323,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536861</v>
+        <v>536704</v>
       </c>
       <c r="R16" t="n">
-        <v>7204835</v>
+        <v>7204580</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2358,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934065</v>
+        <v>119934246</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,21 +2415,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2435,10 +2439,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536683</v>
+        <v>536532</v>
       </c>
       <c r="R17" t="n">
-        <v>7204683</v>
+        <v>7204362</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934041</v>
+        <v>119934064</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>97097</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2519,42 +2523,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536542</v>
+        <v>536851</v>
       </c>
       <c r="R18" t="n">
-        <v>7204366</v>
+        <v>7204845</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934217</v>
+        <v>119934221</v>
       </c>
       <c r="B19" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536771</v>
+        <v>536697</v>
       </c>
       <c r="R19" t="n">
-        <v>7204791</v>
+        <v>7204666</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,21 +2719,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2750,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934030</v>
+        <v>119934216</v>
       </c>
       <c r="B20" t="n">
-        <v>56532</v>
+        <v>90594</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2762,42 +2747,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536532</v>
+        <v>536769</v>
       </c>
       <c r="R20" t="n">
-        <v>7204362</v>
+        <v>7204825</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2829,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,6 +2831,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2866,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934062</v>
+        <v>119934081</v>
       </c>
       <c r="B21" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,25 +2874,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,10 +2902,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536865</v>
+        <v>536882</v>
       </c>
       <c r="R21" t="n">
-        <v>7204832</v>
+        <v>7204819</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2941,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934250</v>
+        <v>119934078</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,21 +2990,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3018,7 +3014,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536603</v>
+        <v>536606</v>
       </c>
       <c r="R22" t="n">
         <v>7204748</v>
@@ -3090,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934216</v>
+        <v>119934114</v>
       </c>
       <c r="B23" t="n">
-        <v>90594</v>
+        <v>94346</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,25 +3098,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>2813</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3130,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536769</v>
+        <v>536852</v>
       </c>
       <c r="R23" t="n">
-        <v>7204825</v>
+        <v>7204836</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3165,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,21 +3182,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3217,7 +3198,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934246</v>
+        <v>119934247</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -3257,10 +3238,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536532</v>
+        <v>536691</v>
       </c>
       <c r="R24" t="n">
-        <v>7204362</v>
+        <v>7204650</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3292,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3302,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,10 +3310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934184</v>
+        <v>119934208</v>
       </c>
       <c r="B25" t="n">
-        <v>94334</v>
+        <v>90576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3341,25 +3322,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3369,10 +3350,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536806</v>
+        <v>536690</v>
       </c>
       <c r="R25" t="n">
-        <v>7204783</v>
+        <v>7204670</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3404,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3414,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3441,10 +3422,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934210</v>
+        <v>119934194</v>
       </c>
       <c r="B26" t="n">
-        <v>74638</v>
+        <v>79659</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3457,21 +3438,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3481,10 +3462,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536837</v>
+        <v>536627</v>
       </c>
       <c r="R26" t="n">
-        <v>7204821</v>
+        <v>7204789</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3516,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3526,7 +3507,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,10 +3534,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934004</v>
+        <v>119934065</v>
       </c>
       <c r="B27" t="n">
-        <v>89650</v>
+        <v>90527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3569,21 +3550,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3574,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536620</v>
+        <v>536683</v>
       </c>
       <c r="R27" t="n">
-        <v>7204779</v>
+        <v>7204683</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3628,7 +3609,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3619,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3649,11 +3630,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3670,10 +3646,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934079</v>
+        <v>119934252</v>
       </c>
       <c r="B28" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3686,21 +3662,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3710,10 +3686,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536847</v>
+        <v>536859</v>
       </c>
       <c r="R28" t="n">
-        <v>7204825</v>
+        <v>7204833</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3745,7 +3721,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3755,7 +3731,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,10 +3758,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934218</v>
+        <v>119934052</v>
       </c>
       <c r="B29" t="n">
-        <v>90594</v>
+        <v>91357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3794,25 +3770,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>918</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3822,10 +3798,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536789</v>
+        <v>536807</v>
       </c>
       <c r="R29" t="n">
-        <v>7204793</v>
+        <v>7204778</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3857,7 +3833,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3867,7 +3843,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3909,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934253</v>
+        <v>119934214</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3925,21 +3901,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3949,10 +3925,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536884</v>
+        <v>536641</v>
       </c>
       <c r="R30" t="n">
-        <v>7204818</v>
+        <v>7204731</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3984,7 +3960,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3994,7 +3970,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4021,10 +3997,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934194</v>
+        <v>119934004</v>
       </c>
       <c r="B31" t="n">
-        <v>79659</v>
+        <v>89650</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,25 +4009,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4061,10 +4037,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536627</v>
+        <v>536620</v>
       </c>
       <c r="R31" t="n">
-        <v>7204789</v>
+        <v>7204779</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4096,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4106,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4117,6 +4093,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4133,10 +4114,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934064</v>
+        <v>119934215</v>
       </c>
       <c r="B32" t="n">
-        <v>97097</v>
+        <v>90594</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4145,25 +4126,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220250</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4173,10 +4154,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536851</v>
+        <v>536591</v>
       </c>
       <c r="R32" t="n">
-        <v>7204845</v>
+        <v>7204751</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4208,7 +4189,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4218,7 +4199,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4245,10 +4226,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934214</v>
+        <v>119934016</v>
       </c>
       <c r="B33" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4261,34 +4242,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536641</v>
+        <v>536575</v>
       </c>
       <c r="R33" t="n">
-        <v>7204731</v>
+        <v>7204458</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4320,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4330,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4357,10 +4343,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934016</v>
+        <v>119934080</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4373,39 +4359,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536575</v>
+        <v>536865</v>
       </c>
       <c r="R34" t="n">
-        <v>7204458</v>
+        <v>7204832</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4437,7 +4418,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4447,7 +4428,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4474,10 +4455,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934249</v>
+        <v>119934041</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4490,34 +4471,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536683</v>
+        <v>536542</v>
       </c>
       <c r="R35" t="n">
-        <v>7204683</v>
+        <v>7204366</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4549,7 +4534,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,7 +4544,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4586,10 +4571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934221</v>
+        <v>119934218</v>
       </c>
       <c r="B36" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4602,21 +4587,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4626,10 +4611,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536697</v>
+        <v>536789</v>
       </c>
       <c r="R36" t="n">
-        <v>7204666</v>
+        <v>7204793</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4661,7 +4646,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4671,7 +4656,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,6 +4667,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4698,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934078</v>
+        <v>119934248</v>
       </c>
       <c r="B37" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536606</v>
+        <v>536694</v>
       </c>
       <c r="R37" t="n">
-        <v>7204748</v>
+        <v>7204667</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4810,10 +4810,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934114</v>
+        <v>119934210</v>
       </c>
       <c r="B38" t="n">
-        <v>94346</v>
+        <v>74638</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2813</v>
+        <v>6439</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536852</v>
+        <v>536837</v>
       </c>
       <c r="R38" t="n">
-        <v>7204836</v>
+        <v>7204821</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4922,10 +4922,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934207</v>
+        <v>119933991</v>
       </c>
       <c r="B39" t="n">
-        <v>90576</v>
+        <v>86074</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4934,25 +4934,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>3294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4962,10 +4962,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536704</v>
+        <v>536861</v>
       </c>
       <c r="R39" t="n">
-        <v>7204580</v>
+        <v>7204835</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5034,10 +5034,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934247</v>
+        <v>119934217</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5050,21 +5050,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536691</v>
+        <v>536771</v>
       </c>
       <c r="R40" t="n">
-        <v>7204650</v>
+        <v>7204791</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5130,6 +5130,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5146,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934066</v>
+        <v>119934137</v>
       </c>
       <c r="B41" t="n">
-        <v>90527</v>
+        <v>74659</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5162,21 +5177,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>112</v>
+        <v>1467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5186,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536771</v>
+        <v>536837</v>
       </c>
       <c r="R41" t="n">
-        <v>7204791</v>
+        <v>7204821</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5221,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5231,7 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5242,21 +5257,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -2623,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934221</v>
+        <v>119934216</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536697</v>
+        <v>536769</v>
       </c>
       <c r="R19" t="n">
-        <v>7204666</v>
+        <v>7204825</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,6 +2719,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2735,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934216</v>
+        <v>119934221</v>
       </c>
       <c r="B20" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2751,21 +2766,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2775,10 +2790,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536769</v>
+        <v>536697</v>
       </c>
       <c r="R20" t="n">
-        <v>7204825</v>
+        <v>7204666</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2810,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2831,21 +2846,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3086,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934114</v>
+        <v>119934247</v>
       </c>
       <c r="B23" t="n">
-        <v>94346</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536852</v>
+        <v>536691</v>
       </c>
       <c r="R23" t="n">
-        <v>7204836</v>
+        <v>7204650</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,10 +3198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934247</v>
+        <v>119934114</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>94346</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3210,25 +3210,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536691</v>
+        <v>536852</v>
       </c>
       <c r="R24" t="n">
-        <v>7204650</v>
+        <v>7204836</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934065</v>
+        <v>119934052</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
+        <v>91357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3546,25 +3546,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>918</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536683</v>
+        <v>536807</v>
       </c>
       <c r="R27" t="n">
-        <v>7204683</v>
+        <v>7204778</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3630,6 +3630,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3646,10 +3661,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934252</v>
+        <v>119934214</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3662,21 +3677,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3686,10 +3701,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536859</v>
+        <v>536641</v>
       </c>
       <c r="R28" t="n">
-        <v>7204833</v>
+        <v>7204731</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3721,7 +3736,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3731,7 +3746,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934052</v>
+        <v>119934065</v>
       </c>
       <c r="B29" t="n">
-        <v>91357</v>
+        <v>90527</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,25 +3785,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>918</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3798,10 +3813,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536807</v>
+        <v>536683</v>
       </c>
       <c r="R29" t="n">
-        <v>7204778</v>
+        <v>7204683</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3833,7 +3848,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3843,7 +3858,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3854,21 +3869,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934214</v>
+        <v>119934252</v>
       </c>
       <c r="B30" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536641</v>
+        <v>536859</v>
       </c>
       <c r="R30" t="n">
-        <v>7204731</v>
+        <v>7204833</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934245</v>
+        <v>119934203</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536407</v>
+        <v>536405</v>
       </c>
       <c r="R2" t="n">
-        <v>7204331</v>
+        <v>7204335</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934203</v>
+        <v>119934015</v>
       </c>
       <c r="B3" t="n">
-        <v>78624</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536405</v>
+        <v>536441</v>
       </c>
       <c r="R3" t="n">
-        <v>7204335</v>
+        <v>7204337</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934014</v>
+        <v>119934009</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536418</v>
+        <v>536410</v>
       </c>
       <c r="R4" t="n">
-        <v>7204363</v>
+        <v>7204341</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934009</v>
+        <v>119934014</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536410</v>
+        <v>536418</v>
       </c>
       <c r="R5" t="n">
-        <v>7204341</v>
+        <v>7204363</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934015</v>
+        <v>119934245</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536441</v>
+        <v>536407</v>
       </c>
       <c r="R6" t="n">
-        <v>7204337</v>
+        <v>7204331</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934066</v>
+        <v>119934248</v>
       </c>
       <c r="B7" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536771</v>
+        <v>536694</v>
       </c>
       <c r="R7" t="n">
-        <v>7204791</v>
+        <v>7204667</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,21 +1341,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1372,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934079</v>
+        <v>119934065</v>
       </c>
       <c r="B8" t="n">
-        <v>79624</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536847</v>
+        <v>536683</v>
       </c>
       <c r="R8" t="n">
-        <v>7204825</v>
+        <v>7204683</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934250</v>
+        <v>119934052</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>91357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>918</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536603</v>
+        <v>536807</v>
       </c>
       <c r="R9" t="n">
-        <v>7204748</v>
+        <v>7204778</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,6 +1565,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934062</v>
+        <v>119934078</v>
       </c>
       <c r="B10" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536865</v>
+        <v>536606</v>
       </c>
       <c r="R10" t="n">
-        <v>7204832</v>
+        <v>7204748</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934030</v>
+        <v>119934218</v>
       </c>
       <c r="B11" t="n">
-        <v>56532</v>
+        <v>90594</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,42 +1720,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536532</v>
+        <v>536789</v>
       </c>
       <c r="R11" t="n">
-        <v>7204362</v>
+        <v>7204793</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,6 +1804,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1824,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934184</v>
+        <v>119934221</v>
       </c>
       <c r="B12" t="n">
-        <v>94334</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,25 +1847,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1864,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536806</v>
+        <v>536697</v>
       </c>
       <c r="R12" t="n">
-        <v>7204783</v>
+        <v>7204666</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,7 +1947,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934249</v>
+        <v>119934252</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1976,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536683</v>
+        <v>536859</v>
       </c>
       <c r="R13" t="n">
-        <v>7204683</v>
+        <v>7204833</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2011,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934251</v>
+        <v>119934247</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2088,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536625</v>
+        <v>536691</v>
       </c>
       <c r="R14" t="n">
-        <v>7204790</v>
+        <v>7204650</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2123,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,21 +2155,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2175,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934253</v>
+        <v>119934207</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,21 +2187,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2215,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536884</v>
+        <v>536704</v>
       </c>
       <c r="R15" t="n">
-        <v>7204818</v>
+        <v>7204580</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2250,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2283,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934207</v>
+        <v>119934004</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>89650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,21 +2299,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2327,10 +2323,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536704</v>
+        <v>536620</v>
       </c>
       <c r="R16" t="n">
-        <v>7204580</v>
+        <v>7204779</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2368,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,6 +2379,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2399,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934246</v>
+        <v>119934184</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,25 +2412,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2439,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536532</v>
+        <v>536806</v>
       </c>
       <c r="R17" t="n">
-        <v>7204362</v>
+        <v>7204783</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934064</v>
+        <v>119934114</v>
       </c>
       <c r="B18" t="n">
-        <v>97097</v>
+        <v>94346</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220250</v>
+        <v>2813</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536851</v>
+        <v>536852</v>
       </c>
       <c r="R18" t="n">
-        <v>7204845</v>
+        <v>7204836</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934216</v>
+        <v>119934081</v>
       </c>
       <c r="B19" t="n">
-        <v>90594</v>
+        <v>79624</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536769</v>
+        <v>536882</v>
       </c>
       <c r="R19" t="n">
-        <v>7204825</v>
+        <v>7204819</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,21 +2720,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2750,10 +2736,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934221</v>
+        <v>119934079</v>
       </c>
       <c r="B20" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,21 +2752,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2790,10 +2776,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536697</v>
+        <v>536847</v>
       </c>
       <c r="R20" t="n">
-        <v>7204666</v>
+        <v>7204825</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2825,7 +2811,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2821,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2848,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934081</v>
+        <v>119934016</v>
       </c>
       <c r="B21" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,34 +2864,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536882</v>
+        <v>536575</v>
       </c>
       <c r="R21" t="n">
-        <v>7204819</v>
+        <v>7204458</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2937,7 +2928,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2938,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,7 +2965,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934078</v>
+        <v>119934080</v>
       </c>
       <c r="B22" t="n">
         <v>79624</v>
@@ -3014,10 +3005,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536606</v>
+        <v>536865</v>
       </c>
       <c r="R22" t="n">
-        <v>7204748</v>
+        <v>7204832</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3049,7 +3040,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3050,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3077,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934247</v>
+        <v>119934030</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,38 +3089,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536691</v>
+        <v>536532</v>
       </c>
       <c r="R23" t="n">
-        <v>7204650</v>
+        <v>7204362</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3161,7 +3156,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3166,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,10 +3193,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934114</v>
+        <v>119934250</v>
       </c>
       <c r="B24" t="n">
-        <v>94346</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3210,25 +3205,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3238,10 +3233,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536852</v>
+        <v>536603</v>
       </c>
       <c r="R24" t="n">
-        <v>7204836</v>
+        <v>7204748</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3273,7 +3268,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3278,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,10 +3305,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934208</v>
+        <v>119934137</v>
       </c>
       <c r="B25" t="n">
-        <v>90576</v>
+        <v>74659</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3326,21 +3321,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3350,10 +3345,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536690</v>
+        <v>536837</v>
       </c>
       <c r="R25" t="n">
-        <v>7204670</v>
+        <v>7204821</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3385,7 +3380,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3390,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,10 +3417,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934194</v>
+        <v>119934208</v>
       </c>
       <c r="B26" t="n">
-        <v>79659</v>
+        <v>90576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3434,25 +3429,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3462,10 +3457,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536627</v>
+        <v>536690</v>
       </c>
       <c r="R26" t="n">
-        <v>7204789</v>
+        <v>7204670</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3497,7 +3492,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,7 +3502,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,10 +3529,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934052</v>
+        <v>119934216</v>
       </c>
       <c r="B27" t="n">
-        <v>91357</v>
+        <v>90594</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3546,25 +3541,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>918</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3574,10 +3569,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536807</v>
+        <v>536769</v>
       </c>
       <c r="R27" t="n">
-        <v>7204778</v>
+        <v>7204825</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3609,7 +3604,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3619,7 +3614,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934214</v>
+        <v>119934064</v>
       </c>
       <c r="B28" t="n">
-        <v>90594</v>
+        <v>97097</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3673,25 +3668,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>220250</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3701,10 +3696,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536641</v>
+        <v>536851</v>
       </c>
       <c r="R28" t="n">
-        <v>7204731</v>
+        <v>7204845</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3736,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3746,7 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,10 +3768,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934065</v>
+        <v>119934246</v>
       </c>
       <c r="B29" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3789,21 +3784,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3813,10 +3808,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536683</v>
+        <v>536532</v>
       </c>
       <c r="R29" t="n">
-        <v>7204683</v>
+        <v>7204362</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3848,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3858,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934252</v>
+        <v>119934062</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3897,25 +3892,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3925,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536859</v>
+        <v>536865</v>
       </c>
       <c r="R30" t="n">
-        <v>7204833</v>
+        <v>7204832</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3997,10 +3992,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934004</v>
+        <v>119934041</v>
       </c>
       <c r="B31" t="n">
-        <v>89650</v>
+        <v>57473</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4013,34 +4008,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536620</v>
+        <v>536542</v>
       </c>
       <c r="R31" t="n">
-        <v>7204779</v>
+        <v>7204366</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4072,7 +4071,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4081,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4093,11 +4092,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4114,10 +4108,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934215</v>
+        <v>119934249</v>
       </c>
       <c r="B32" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4130,21 +4124,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4154,10 +4148,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536591</v>
+        <v>536683</v>
       </c>
       <c r="R32" t="n">
-        <v>7204751</v>
+        <v>7204683</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4189,7 +4183,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4199,7 +4193,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4226,10 +4220,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934016</v>
+        <v>119934194</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>79659</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4238,43 +4232,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536575</v>
+        <v>536627</v>
       </c>
       <c r="R33" t="n">
-        <v>7204458</v>
+        <v>7204789</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4306,7 +4295,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4305,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,10 +4332,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934080</v>
+        <v>119934253</v>
       </c>
       <c r="B34" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4359,21 +4348,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4383,10 +4372,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536865</v>
+        <v>536884</v>
       </c>
       <c r="R34" t="n">
-        <v>7204832</v>
+        <v>7204818</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4418,7 +4407,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4428,7 +4417,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,10 +4444,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934041</v>
+        <v>119934066</v>
       </c>
       <c r="B35" t="n">
-        <v>57473</v>
+        <v>90527</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4471,38 +4460,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536542</v>
+        <v>536771</v>
       </c>
       <c r="R35" t="n">
-        <v>7204366</v>
+        <v>7204791</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4534,7 +4519,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4544,7 +4529,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4555,6 +4540,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4571,10 +4571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934218</v>
+        <v>119933991</v>
       </c>
       <c r="B36" t="n">
-        <v>90594</v>
+        <v>86074</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4583,25 +4583,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>3294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536789</v>
+        <v>536861</v>
       </c>
       <c r="R36" t="n">
-        <v>7204793</v>
+        <v>7204835</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4667,21 +4667,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4698,7 +4683,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934248</v>
+        <v>119934251</v>
       </c>
       <c r="B37" t="n">
         <v>78542</v>
@@ -4738,10 +4723,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536694</v>
+        <v>536625</v>
       </c>
       <c r="R37" t="n">
-        <v>7204667</v>
+        <v>7204790</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4773,7 +4758,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4783,7 +4768,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4794,6 +4779,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4810,10 +4810,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934210</v>
+        <v>119934215</v>
       </c>
       <c r="B38" t="n">
-        <v>74638</v>
+        <v>90594</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4822,25 +4822,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6439</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536837</v>
+        <v>536591</v>
       </c>
       <c r="R38" t="n">
-        <v>7204821</v>
+        <v>7204751</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4922,10 +4922,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119933991</v>
+        <v>119934214</v>
       </c>
       <c r="B39" t="n">
-        <v>86074</v>
+        <v>90594</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4934,25 +4934,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3294</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4962,10 +4962,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536861</v>
+        <v>536641</v>
       </c>
       <c r="R39" t="n">
-        <v>7204835</v>
+        <v>7204731</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5161,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934137</v>
+        <v>119934210</v>
       </c>
       <c r="B41" t="n">
-        <v>74659</v>
+        <v>74638</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5173,25 +5173,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>6439</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934203</v>
+        <v>119934014</v>
       </c>
       <c r="B2" t="n">
-        <v>78624</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536405</v>
+        <v>536418</v>
       </c>
       <c r="R2" t="n">
-        <v>7204335</v>
+        <v>7204363</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934015</v>
+        <v>119934245</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536441</v>
+        <v>536407</v>
       </c>
       <c r="R3" t="n">
-        <v>7204337</v>
+        <v>7204331</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934009</v>
+        <v>119934203</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>78624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536410</v>
+        <v>536405</v>
       </c>
       <c r="R4" t="n">
-        <v>7204341</v>
+        <v>7204335</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934014</v>
+        <v>119934009</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536418</v>
+        <v>536410</v>
       </c>
       <c r="R5" t="n">
-        <v>7204363</v>
+        <v>7204341</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934245</v>
+        <v>119934015</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536407</v>
+        <v>536441</v>
       </c>
       <c r="R6" t="n">
-        <v>7204331</v>
+        <v>7204337</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934248</v>
+        <v>119934004</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536694</v>
+        <v>536620</v>
       </c>
       <c r="R7" t="n">
-        <v>7204667</v>
+        <v>7204779</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,6 +1341,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934065</v>
+        <v>119934251</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536683</v>
+        <v>536625</v>
       </c>
       <c r="R8" t="n">
-        <v>7204683</v>
+        <v>7204790</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,6 +1458,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1596,7 +1616,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934078</v>
+        <v>119934079</v>
       </c>
       <c r="B10" t="n">
         <v>79624</v>
@@ -1636,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536606</v>
+        <v>536847</v>
       </c>
       <c r="R10" t="n">
-        <v>7204748</v>
+        <v>7204825</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934218</v>
+        <v>119934210</v>
       </c>
       <c r="B11" t="n">
-        <v>90594</v>
+        <v>74638</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,25 +1740,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536789</v>
+        <v>536837</v>
       </c>
       <c r="R11" t="n">
-        <v>7204793</v>
+        <v>7204821</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,21 +1824,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1835,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934221</v>
+        <v>119934030</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>56532</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,38 +1852,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536697</v>
+        <v>536532</v>
       </c>
       <c r="R12" t="n">
-        <v>7204666</v>
+        <v>7204362</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1910,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +1956,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934252</v>
+        <v>119934217</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,21 +1972,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1996,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536859</v>
+        <v>536771</v>
       </c>
       <c r="R13" t="n">
-        <v>7204833</v>
+        <v>7204791</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2022,7 +2031,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2041,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,6 +2052,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2059,7 +2083,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934247</v>
+        <v>119934249</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2099,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536691</v>
+        <v>536683</v>
       </c>
       <c r="R14" t="n">
-        <v>7204650</v>
+        <v>7204683</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2134,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2168,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934207</v>
+        <v>119934081</v>
       </c>
       <c r="B15" t="n">
-        <v>90576</v>
+        <v>79624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2211,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536704</v>
+        <v>536882</v>
       </c>
       <c r="R15" t="n">
-        <v>7204580</v>
+        <v>7204819</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2246,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2280,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934004</v>
+        <v>119934207</v>
       </c>
       <c r="B16" t="n">
-        <v>89650</v>
+        <v>90576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,21 +2323,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2323,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536620</v>
+        <v>536704</v>
       </c>
       <c r="R16" t="n">
-        <v>7204779</v>
+        <v>7204580</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2358,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,7 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,11 +2403,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2400,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934184</v>
+        <v>119934214</v>
       </c>
       <c r="B17" t="n">
-        <v>94334</v>
+        <v>90594</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,25 +2431,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2440,10 +2459,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536806</v>
+        <v>536641</v>
       </c>
       <c r="R17" t="n">
-        <v>7204783</v>
+        <v>7204731</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2475,7 +2494,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2504,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934114</v>
+        <v>119934218</v>
       </c>
       <c r="B18" t="n">
-        <v>94346</v>
+        <v>90594</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,25 +2543,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2813</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536852</v>
+        <v>536789</v>
       </c>
       <c r="R18" t="n">
-        <v>7204836</v>
+        <v>7204793</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2587,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,6 +2627,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2624,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934081</v>
+        <v>119934216</v>
       </c>
       <c r="B19" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2640,21 +2674,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2698,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536882</v>
+        <v>536769</v>
       </c>
       <c r="R19" t="n">
-        <v>7204819</v>
+        <v>7204825</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2699,7 +2733,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2743,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,6 +2754,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2736,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934079</v>
+        <v>119934114</v>
       </c>
       <c r="B20" t="n">
-        <v>79624</v>
+        <v>94346</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,25 +2797,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>2813</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2776,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536847</v>
+        <v>536852</v>
       </c>
       <c r="R20" t="n">
-        <v>7204825</v>
+        <v>7204836</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2811,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,7 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934016</v>
+        <v>119934065</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2864,39 +2913,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536575</v>
+        <v>536683</v>
       </c>
       <c r="R21" t="n">
-        <v>7204458</v>
+        <v>7204683</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2928,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2938,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934080</v>
+        <v>119934062</v>
       </c>
       <c r="B22" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2977,25 +3021,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3077,10 +3121,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934030</v>
+        <v>119934250</v>
       </c>
       <c r="B23" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3089,42 +3133,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536532</v>
+        <v>536603</v>
       </c>
       <c r="R23" t="n">
-        <v>7204362</v>
+        <v>7204748</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3156,7 +3196,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3166,7 +3206,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,7 +3233,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934250</v>
+        <v>119934247</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -3233,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536603</v>
+        <v>536691</v>
       </c>
       <c r="R24" t="n">
-        <v>7204748</v>
+        <v>7204650</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3268,7 +3308,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3278,7 +3318,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934137</v>
+        <v>119934080</v>
       </c>
       <c r="B25" t="n">
-        <v>74659</v>
+        <v>79624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,21 +3361,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3345,10 +3385,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536837</v>
+        <v>536865</v>
       </c>
       <c r="R25" t="n">
-        <v>7204821</v>
+        <v>7204832</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3380,7 +3420,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3390,7 +3430,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3417,10 +3457,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934208</v>
+        <v>119933991</v>
       </c>
       <c r="B26" t="n">
-        <v>90576</v>
+        <v>86074</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3429,25 +3469,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>3294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3457,10 +3497,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536690</v>
+        <v>536861</v>
       </c>
       <c r="R26" t="n">
-        <v>7204670</v>
+        <v>7204835</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3492,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3502,7 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934216</v>
+        <v>119934066</v>
       </c>
       <c r="B27" t="n">
-        <v>90594</v>
+        <v>90527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3545,21 +3585,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3569,10 +3609,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536769</v>
+        <v>536771</v>
       </c>
       <c r="R27" t="n">
-        <v>7204825</v>
+        <v>7204791</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3604,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3614,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,10 +3696,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934064</v>
+        <v>119934248</v>
       </c>
       <c r="B28" t="n">
-        <v>97097</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,25 +3708,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220250</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3696,10 +3736,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536851</v>
+        <v>536694</v>
       </c>
       <c r="R28" t="n">
-        <v>7204845</v>
+        <v>7204667</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3731,7 +3771,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3781,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,10 +3808,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934246</v>
+        <v>119934078</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3784,21 +3824,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3808,10 +3848,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536532</v>
+        <v>536606</v>
       </c>
       <c r="R29" t="n">
-        <v>7204362</v>
+        <v>7204748</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3843,7 +3883,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3893,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3920,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934062</v>
+        <v>119934194</v>
       </c>
       <c r="B30" t="n">
-        <v>79652</v>
+        <v>79659</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,21 +3936,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3960,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536865</v>
+        <v>536627</v>
       </c>
       <c r="R30" t="n">
-        <v>7204832</v>
+        <v>7204789</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3955,7 +3995,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +4005,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3992,10 +4032,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934041</v>
+        <v>119934215</v>
       </c>
       <c r="B31" t="n">
-        <v>57473</v>
+        <v>90594</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4008,38 +4048,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536542</v>
+        <v>536591</v>
       </c>
       <c r="R31" t="n">
-        <v>7204366</v>
+        <v>7204751</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4071,7 +4107,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4081,7 +4117,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4108,10 +4144,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934249</v>
+        <v>119934208</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4124,21 +4160,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4148,10 +4184,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536683</v>
+        <v>536690</v>
       </c>
       <c r="R32" t="n">
-        <v>7204683</v>
+        <v>7204670</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4183,7 +4219,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4193,7 +4229,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4220,10 +4256,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934194</v>
+        <v>119934064</v>
       </c>
       <c r="B33" t="n">
-        <v>79659</v>
+        <v>97097</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4236,21 +4272,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>220250</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4260,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536627</v>
+        <v>536851</v>
       </c>
       <c r="R33" t="n">
-        <v>7204789</v>
+        <v>7204845</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4295,7 +4331,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4305,7 +4341,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4332,10 +4368,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934253</v>
+        <v>119934016</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4348,34 +4384,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536884</v>
+        <v>536575</v>
       </c>
       <c r="R34" t="n">
-        <v>7204818</v>
+        <v>7204458</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4407,7 +4448,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4417,7 +4458,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4444,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934066</v>
+        <v>119934184</v>
       </c>
       <c r="B35" t="n">
-        <v>90527</v>
+        <v>94334</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4456,25 +4497,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>112</v>
+        <v>2809</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4484,10 +4525,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536771</v>
+        <v>536806</v>
       </c>
       <c r="R35" t="n">
-        <v>7204791</v>
+        <v>7204783</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4519,7 +4560,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4529,7 +4570,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4540,21 +4581,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4571,10 +4597,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119933991</v>
+        <v>119934253</v>
       </c>
       <c r="B36" t="n">
-        <v>86074</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4583,25 +4609,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3294</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4611,10 +4637,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536861</v>
+        <v>536884</v>
       </c>
       <c r="R36" t="n">
-        <v>7204835</v>
+        <v>7204818</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4646,7 +4672,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4656,7 +4682,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4683,10 +4709,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934251</v>
+        <v>119934041</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4699,34 +4725,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536625</v>
+        <v>536542</v>
       </c>
       <c r="R37" t="n">
-        <v>7204790</v>
+        <v>7204366</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4758,7 +4788,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4768,7 +4798,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4779,21 +4809,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4810,10 +4825,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934215</v>
+        <v>119934221</v>
       </c>
       <c r="B38" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4826,21 +4841,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4850,10 +4865,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536591</v>
+        <v>536697</v>
       </c>
       <c r="R38" t="n">
-        <v>7204751</v>
+        <v>7204666</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4885,7 +4900,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4895,7 +4910,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4922,10 +4937,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934214</v>
+        <v>119934137</v>
       </c>
       <c r="B39" t="n">
-        <v>90594</v>
+        <v>74659</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4938,21 +4953,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4962,10 +4977,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536641</v>
+        <v>536837</v>
       </c>
       <c r="R39" t="n">
-        <v>7204731</v>
+        <v>7204821</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4997,7 +5012,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5007,7 +5022,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5034,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934217</v>
+        <v>119934252</v>
       </c>
       <c r="B40" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5050,21 +5065,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5074,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536771</v>
+        <v>536859</v>
       </c>
       <c r="R40" t="n">
-        <v>7204791</v>
+        <v>7204833</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5109,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5119,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5130,21 +5145,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5161,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934210</v>
+        <v>119934246</v>
       </c>
       <c r="B41" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5173,25 +5173,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536837</v>
+        <v>536532</v>
       </c>
       <c r="R41" t="n">
-        <v>7204821</v>
+        <v>7204362</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -1840,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934030</v>
+        <v>119934217</v>
       </c>
       <c r="B12" t="n">
-        <v>56532</v>
+        <v>90594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,42 +1852,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536532</v>
+        <v>536771</v>
       </c>
       <c r="R12" t="n">
-        <v>7204362</v>
+        <v>7204791</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1919,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1929,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,6 +1936,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1956,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934217</v>
+        <v>119934030</v>
       </c>
       <c r="B13" t="n">
-        <v>90594</v>
+        <v>56532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,38 +1979,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536771</v>
+        <v>536532</v>
       </c>
       <c r="R13" t="n">
-        <v>7204791</v>
+        <v>7204362</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2031,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2041,7 +2056,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,21 +2067,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934249</v>
+        <v>119934081</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,21 +2099,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536683</v>
+        <v>536882</v>
       </c>
       <c r="R14" t="n">
-        <v>7204683</v>
+        <v>7204819</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934081</v>
+        <v>119934249</v>
       </c>
       <c r="B15" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536882</v>
+        <v>536683</v>
       </c>
       <c r="R15" t="n">
-        <v>7204819</v>
+        <v>7204683</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3808,10 +3808,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934078</v>
+        <v>119934194</v>
       </c>
       <c r="B29" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3820,25 +3820,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536606</v>
+        <v>536627</v>
       </c>
       <c r="R29" t="n">
-        <v>7204748</v>
+        <v>7204789</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3920,10 +3920,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934194</v>
+        <v>119934215</v>
       </c>
       <c r="B30" t="n">
-        <v>79659</v>
+        <v>90594</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3932,25 +3932,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3960,10 +3960,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536627</v>
+        <v>536591</v>
       </c>
       <c r="R30" t="n">
-        <v>7204789</v>
+        <v>7204751</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4032,10 +4032,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934215</v>
+        <v>119934208</v>
       </c>
       <c r="B31" t="n">
-        <v>90594</v>
+        <v>90576</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4048,21 +4048,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536591</v>
+        <v>536690</v>
       </c>
       <c r="R31" t="n">
-        <v>7204751</v>
+        <v>7204670</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934208</v>
+        <v>119934078</v>
       </c>
       <c r="B32" t="n">
-        <v>90576</v>
+        <v>79624</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536690</v>
+        <v>536606</v>
       </c>
       <c r="R32" t="n">
-        <v>7204670</v>
+        <v>7204748</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4597,10 +4597,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934253</v>
+        <v>119934041</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4613,34 +4613,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536884</v>
+        <v>536542</v>
       </c>
       <c r="R36" t="n">
-        <v>7204818</v>
+        <v>7204366</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4672,7 +4676,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4682,7 +4686,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4709,10 +4713,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934041</v>
+        <v>119934221</v>
       </c>
       <c r="B37" t="n">
-        <v>57473</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4725,38 +4729,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536542</v>
+        <v>536697</v>
       </c>
       <c r="R37" t="n">
-        <v>7204366</v>
+        <v>7204666</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4825,10 +4825,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934221</v>
+        <v>119934253</v>
       </c>
       <c r="B38" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4841,21 +4841,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536697</v>
+        <v>536884</v>
       </c>
       <c r="R38" t="n">
-        <v>7204666</v>
+        <v>7204818</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934245</v>
+        <v>119934015</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536407</v>
+        <v>536441</v>
       </c>
       <c r="R3" t="n">
-        <v>7204331</v>
+        <v>7204337</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934015</v>
+        <v>119934245</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536441</v>
+        <v>536407</v>
       </c>
       <c r="R6" t="n">
-        <v>7204337</v>
+        <v>7204331</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934004</v>
+        <v>119934250</v>
       </c>
       <c r="B7" t="n">
-        <v>89650</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536620</v>
+        <v>536603</v>
       </c>
       <c r="R7" t="n">
-        <v>7204779</v>
+        <v>7204748</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,11 +1341,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934251</v>
+        <v>119934080</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536625</v>
+        <v>536865</v>
       </c>
       <c r="R8" t="n">
-        <v>7204790</v>
+        <v>7204832</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,21 +1453,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1489,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934052</v>
+        <v>119934221</v>
       </c>
       <c r="B9" t="n">
-        <v>91357</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536807</v>
+        <v>536697</v>
       </c>
       <c r="R9" t="n">
-        <v>7204778</v>
+        <v>7204666</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1564,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,21 +1565,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1616,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934079</v>
+        <v>119934064</v>
       </c>
       <c r="B10" t="n">
-        <v>79624</v>
+        <v>97097</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,25 +1593,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>220250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536847</v>
+        <v>536851</v>
       </c>
       <c r="R10" t="n">
-        <v>7204825</v>
+        <v>7204845</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1691,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934210</v>
+        <v>119934253</v>
       </c>
       <c r="B11" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536837</v>
+        <v>536884</v>
       </c>
       <c r="R11" t="n">
-        <v>7204821</v>
+        <v>7204818</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934217</v>
+        <v>119933991</v>
       </c>
       <c r="B12" t="n">
-        <v>90594</v>
+        <v>86074</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,25 +1817,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>3294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536771</v>
+        <v>536861</v>
       </c>
       <c r="R12" t="n">
-        <v>7204791</v>
+        <v>7204835</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,21 +1901,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1967,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934030</v>
+        <v>119934246</v>
       </c>
       <c r="B13" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,32 +1929,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
@@ -2083,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934081</v>
+        <v>119934217</v>
       </c>
       <c r="B14" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2123,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536882</v>
+        <v>536771</v>
       </c>
       <c r="R14" t="n">
-        <v>7204819</v>
+        <v>7204791</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2158,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,6 +2125,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2195,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934249</v>
+        <v>119934079</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,21 +2172,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2235,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536683</v>
+        <v>536847</v>
       </c>
       <c r="R15" t="n">
-        <v>7204683</v>
+        <v>7204825</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2270,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934207</v>
+        <v>119934194</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>79659</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,25 +2280,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2347,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536704</v>
+        <v>536627</v>
       </c>
       <c r="R16" t="n">
-        <v>7204580</v>
+        <v>7204789</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2382,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934214</v>
+        <v>119934210</v>
       </c>
       <c r="B17" t="n">
-        <v>90594</v>
+        <v>74638</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,25 +2392,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6439</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2459,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536641</v>
+        <v>536837</v>
       </c>
       <c r="R17" t="n">
-        <v>7204731</v>
+        <v>7204821</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2494,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934218</v>
+        <v>119934081</v>
       </c>
       <c r="B18" t="n">
-        <v>90594</v>
+        <v>79624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,21 +2508,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2571,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536789</v>
+        <v>536882</v>
       </c>
       <c r="R18" t="n">
-        <v>7204793</v>
+        <v>7204819</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2606,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,21 +2588,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2658,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934216</v>
+        <v>119934208</v>
       </c>
       <c r="B19" t="n">
-        <v>90594</v>
+        <v>90576</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,21 +2620,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2698,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536769</v>
+        <v>536690</v>
       </c>
       <c r="R19" t="n">
-        <v>7204825</v>
+        <v>7204670</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2733,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2743,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,21 +2700,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2785,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934114</v>
+        <v>119934078</v>
       </c>
       <c r="B20" t="n">
-        <v>94346</v>
+        <v>79624</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2797,25 +2728,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2825,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536852</v>
+        <v>536606</v>
       </c>
       <c r="R20" t="n">
-        <v>7204836</v>
+        <v>7204748</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2860,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934065</v>
+        <v>119934052</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>91357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2909,25 +2840,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>918</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2937,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536683</v>
+        <v>536807</v>
       </c>
       <c r="R21" t="n">
-        <v>7204683</v>
+        <v>7204778</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2972,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,6 +2924,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3009,10 +2955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934062</v>
+        <v>119934247</v>
       </c>
       <c r="B22" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3021,25 +2967,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3049,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536865</v>
+        <v>536691</v>
       </c>
       <c r="R22" t="n">
-        <v>7204832</v>
+        <v>7204650</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3084,7 +3030,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3040,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3121,7 +3067,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934250</v>
+        <v>119934248</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -3161,10 +3107,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536603</v>
+        <v>536694</v>
       </c>
       <c r="R23" t="n">
-        <v>7204748</v>
+        <v>7204667</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3196,7 +3142,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3152,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3179,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934247</v>
+        <v>119934016</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,34 +3195,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536691</v>
+        <v>536575</v>
       </c>
       <c r="R24" t="n">
-        <v>7204650</v>
+        <v>7204458</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3308,7 +3259,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3318,7 +3269,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,10 +3296,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934080</v>
+        <v>119934066</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>90527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3361,21 +3312,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3385,10 +3336,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536865</v>
+        <v>536771</v>
       </c>
       <c r="R25" t="n">
-        <v>7204832</v>
+        <v>7204791</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3420,7 +3371,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3430,7 +3381,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3441,6 +3392,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3457,10 +3423,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119933991</v>
+        <v>119934041</v>
       </c>
       <c r="B26" t="n">
-        <v>86074</v>
+        <v>57473</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3469,38 +3435,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3294</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536861</v>
+        <v>536542</v>
       </c>
       <c r="R26" t="n">
-        <v>7204835</v>
+        <v>7204366</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3532,7 +3502,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,7 +3512,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,10 +3539,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934066</v>
+        <v>119934062</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
+        <v>79652</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,25 +3551,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3609,10 +3579,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536771</v>
+        <v>536865</v>
       </c>
       <c r="R27" t="n">
-        <v>7204791</v>
+        <v>7204832</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3644,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,21 +3635,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3696,10 +3651,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934248</v>
+        <v>119934216</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3712,21 +3667,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3736,10 +3691,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536694</v>
+        <v>536769</v>
       </c>
       <c r="R28" t="n">
-        <v>7204667</v>
+        <v>7204825</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3771,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3781,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3792,6 +3747,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3808,10 +3778,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934194</v>
+        <v>119934207</v>
       </c>
       <c r="B29" t="n">
-        <v>79659</v>
+        <v>90576</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3820,25 +3790,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3848,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536627</v>
+        <v>536704</v>
       </c>
       <c r="R29" t="n">
-        <v>7204789</v>
+        <v>7204580</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3883,7 +3853,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3893,7 +3863,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3920,10 +3890,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934215</v>
+        <v>119934004</v>
       </c>
       <c r="B30" t="n">
-        <v>90594</v>
+        <v>89650</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3936,21 +3906,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3960,10 +3930,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536591</v>
+        <v>536620</v>
       </c>
       <c r="R30" t="n">
-        <v>7204751</v>
+        <v>7204779</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3995,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4005,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4016,6 +3986,11 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4032,10 +4007,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934208</v>
+        <v>119934252</v>
       </c>
       <c r="B31" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4048,21 +4023,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4072,10 +4047,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536690</v>
+        <v>536859</v>
       </c>
       <c r="R31" t="n">
-        <v>7204670</v>
+        <v>7204833</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4107,7 +4082,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4117,7 +4092,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4144,10 +4119,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934078</v>
+        <v>119934137</v>
       </c>
       <c r="B32" t="n">
-        <v>79624</v>
+        <v>74659</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4160,21 +4135,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4184,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536606</v>
+        <v>536837</v>
       </c>
       <c r="R32" t="n">
-        <v>7204748</v>
+        <v>7204821</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4219,7 +4194,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4229,7 +4204,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4256,10 +4231,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934064</v>
+        <v>119934218</v>
       </c>
       <c r="B33" t="n">
-        <v>97097</v>
+        <v>90594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4268,25 +4243,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220250</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4296,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536851</v>
+        <v>536789</v>
       </c>
       <c r="R33" t="n">
-        <v>7204845</v>
+        <v>7204793</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4331,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4341,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4352,6 +4327,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4368,10 +4358,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934016</v>
+        <v>119934030</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4380,31 +4370,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4413,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536575</v>
+        <v>536532</v>
       </c>
       <c r="R34" t="n">
-        <v>7204458</v>
+        <v>7204362</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4448,7 +4437,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4458,7 +4447,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4485,10 +4474,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934184</v>
+        <v>119934114</v>
       </c>
       <c r="B35" t="n">
-        <v>94334</v>
+        <v>94346</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4501,21 +4490,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4525,10 +4514,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536806</v>
+        <v>536852</v>
       </c>
       <c r="R35" t="n">
-        <v>7204783</v>
+        <v>7204836</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4560,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4570,7 +4559,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4597,10 +4586,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934041</v>
+        <v>119934251</v>
       </c>
       <c r="B36" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4613,38 +4602,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536542</v>
+        <v>536625</v>
       </c>
       <c r="R36" t="n">
-        <v>7204366</v>
+        <v>7204790</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4676,7 +4661,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4686,7 +4671,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4697,6 +4682,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4713,10 +4713,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934221</v>
+        <v>119934249</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4729,21 +4729,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536697</v>
+        <v>536683</v>
       </c>
       <c r="R37" t="n">
-        <v>7204666</v>
+        <v>7204683</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4825,10 +4825,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934253</v>
+        <v>119934184</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4837,25 +4837,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536884</v>
+        <v>536806</v>
       </c>
       <c r="R38" t="n">
-        <v>7204818</v>
+        <v>7204783</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4937,10 +4937,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934137</v>
+        <v>119934214</v>
       </c>
       <c r="B39" t="n">
-        <v>74659</v>
+        <v>90594</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4953,21 +4953,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536837</v>
+        <v>536641</v>
       </c>
       <c r="R39" t="n">
-        <v>7204821</v>
+        <v>7204731</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5049,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934252</v>
+        <v>119934215</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5065,21 +5065,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536859</v>
+        <v>536591</v>
       </c>
       <c r="R40" t="n">
-        <v>7204833</v>
+        <v>7204751</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934246</v>
+        <v>119934065</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>90527</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>536532</v>
+        <v>536683</v>
       </c>
       <c r="R41" t="n">
-        <v>7204362</v>
+        <v>7204683</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 28669-2024 artfynd.xlsx
+++ b/artfynd/A 28669-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934014</v>
+        <v>119934203</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536418</v>
+        <v>536405</v>
       </c>
       <c r="R2" t="n">
-        <v>7204363</v>
+        <v>7204335</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934015</v>
+        <v>119934009</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536441</v>
+        <v>536410</v>
       </c>
       <c r="R3" t="n">
-        <v>7204337</v>
+        <v>7204341</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934203</v>
+        <v>119934245</v>
       </c>
       <c r="B4" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536405</v>
+        <v>536407</v>
       </c>
       <c r="R4" t="n">
-        <v>7204335</v>
+        <v>7204331</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934009</v>
+        <v>119934014</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536410</v>
+        <v>536418</v>
       </c>
       <c r="R5" t="n">
-        <v>7204341</v>
+        <v>7204363</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934245</v>
+        <v>119934015</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536407</v>
+        <v>536441</v>
       </c>
       <c r="R6" t="n">
-        <v>7204331</v>
+        <v>7204337</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934250</v>
+        <v>119934030</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,38 +1257,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536603</v>
+        <v>536532</v>
       </c>
       <c r="R7" t="n">
-        <v>7204748</v>
+        <v>7204362</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934080</v>
+        <v>119934215</v>
       </c>
       <c r="B8" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536865</v>
+        <v>536591</v>
       </c>
       <c r="R8" t="n">
-        <v>7204832</v>
+        <v>7204751</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934221</v>
+        <v>119934114</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>94346</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1485,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2813</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536697</v>
+        <v>536852</v>
       </c>
       <c r="R9" t="n">
-        <v>7204666</v>
+        <v>7204836</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934064</v>
+        <v>119934251</v>
       </c>
       <c r="B10" t="n">
-        <v>97097</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1597,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220250</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536851</v>
+        <v>536625</v>
       </c>
       <c r="R10" t="n">
-        <v>7204845</v>
+        <v>7204790</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,6 +1681,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1693,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934253</v>
+        <v>119934248</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1733,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536884</v>
+        <v>536694</v>
       </c>
       <c r="R11" t="n">
-        <v>7204818</v>
+        <v>7204667</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119933991</v>
+        <v>119934016</v>
       </c>
       <c r="B12" t="n">
-        <v>86074</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,38 +1836,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3294</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536861</v>
+        <v>536575</v>
       </c>
       <c r="R12" t="n">
-        <v>7204835</v>
+        <v>7204458</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934246</v>
+        <v>119934221</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,21 +1957,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536532</v>
+        <v>536697</v>
       </c>
       <c r="R13" t="n">
-        <v>7204362</v>
+        <v>7204666</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934217</v>
+        <v>119934247</v>
       </c>
       <c r="B14" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,21 +2069,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536771</v>
+        <v>536691</v>
       </c>
       <c r="R14" t="n">
-        <v>7204791</v>
+        <v>7204650</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,21 +2149,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2156,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119934079</v>
+        <v>119934217</v>
       </c>
       <c r="B15" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,21 +2181,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536847</v>
+        <v>536771</v>
       </c>
       <c r="R15" t="n">
-        <v>7204825</v>
+        <v>7204791</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,6 +2261,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2268,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934194</v>
+        <v>119934210</v>
       </c>
       <c r="B16" t="n">
-        <v>79659</v>
+        <v>74638</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,21 +2308,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536627</v>
+        <v>536837</v>
       </c>
       <c r="R16" t="n">
-        <v>7204789</v>
+        <v>7204821</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934210</v>
+        <v>119934052</v>
       </c>
       <c r="B17" t="n">
-        <v>74638</v>
+        <v>91357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,25 +2416,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6439</v>
+        <v>918</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2444,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536837</v>
+        <v>536807</v>
       </c>
       <c r="R17" t="n">
-        <v>7204821</v>
+        <v>7204778</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2479,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2489,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,6 +2500,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2492,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934081</v>
+        <v>119934064</v>
       </c>
       <c r="B18" t="n">
-        <v>79624</v>
+        <v>97097</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,25 +2543,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>220250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536882</v>
+        <v>536851</v>
       </c>
       <c r="R18" t="n">
-        <v>7204819</v>
+        <v>7204845</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2643,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934208</v>
+        <v>119934246</v>
       </c>
       <c r="B19" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,21 +2659,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2683,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536690</v>
+        <v>536532</v>
       </c>
       <c r="R19" t="n">
-        <v>7204670</v>
+        <v>7204362</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2755,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934078</v>
+        <v>119934218</v>
       </c>
       <c r="B20" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,21 +2771,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2795,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536606</v>
+        <v>536789</v>
       </c>
       <c r="R20" t="n">
-        <v>7204748</v>
+        <v>7204793</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2830,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2840,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,6 +2851,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2828,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934052</v>
+        <v>119934062</v>
       </c>
       <c r="B21" t="n">
-        <v>91357</v>
+        <v>79652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2840,25 +2894,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>918</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2868,10 +2922,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536807</v>
+        <v>536865</v>
       </c>
       <c r="R21" t="n">
-        <v>7204778</v>
+        <v>7204832</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2903,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2967,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,21 +2978,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2955,10 +2994,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934247</v>
+        <v>119934207</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,21 +3010,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2995,10 +3034,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536691</v>
+        <v>536704</v>
       </c>
       <c r="R22" t="n">
-        <v>7204650</v>
+        <v>7204580</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3030,7 +3069,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3040,7 +3079,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3067,7 +3106,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934248</v>
+        <v>119934253</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -3107,10 +3146,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536694</v>
+        <v>536884</v>
       </c>
       <c r="R23" t="n">
-        <v>7204667</v>
+        <v>7204818</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3142,7 +3181,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3152,7 +3191,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3179,10 +3218,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934016</v>
+        <v>119934081</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3195,39 +3234,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536575</v>
+        <v>536882</v>
       </c>
       <c r="R24" t="n">
-        <v>7204458</v>
+        <v>7204819</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3259,7 +3293,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3269,7 +3303,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3296,10 +3330,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934066</v>
+        <v>119934184</v>
       </c>
       <c r="B25" t="n">
-        <v>90527</v>
+        <v>94334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3308,25 +3342,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3336,10 +3370,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536771</v>
+        <v>536806</v>
       </c>
       <c r="R25" t="n">
-        <v>7204791</v>
+        <v>7204783</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3371,7 +3405,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3381,7 +3415,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,21 +3426,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3423,10 +3442,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934041</v>
+        <v>119934214</v>
       </c>
       <c r="B26" t="n">
-        <v>57473</v>
+        <v>90594</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3439,38 +3458,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536542</v>
+        <v>536641</v>
       </c>
       <c r="R26" t="n">
-        <v>7204366</v>
+        <v>7204731</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3502,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3512,7 +3527,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,10 +3554,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934062</v>
+        <v>119934194</v>
       </c>
       <c r="B27" t="n">
-        <v>79652</v>
+        <v>79659</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3555,21 +3570,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3579,10 +3594,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536865</v>
+        <v>536627</v>
       </c>
       <c r="R27" t="n">
-        <v>7204832</v>
+        <v>7204789</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3614,7 +3629,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3639,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,10 +3666,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934216</v>
+        <v>119934041</v>
       </c>
       <c r="B28" t="n">
-        <v>90594</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3667,34 +3682,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536769</v>
+        <v>536542</v>
       </c>
       <c r="R28" t="n">
-        <v>7204825</v>
+        <v>7204366</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3726,7 +3745,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3755,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3747,21 +3766,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3778,10 +3782,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934207</v>
+        <v>119934004</v>
       </c>
       <c r="B29" t="n">
-        <v>90576</v>
+        <v>89650</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3794,21 +3798,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3822,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>536704</v>
+        <v>536620</v>
       </c>
       <c r="R29" t="n">
-        <v>7204580</v>
+        <v>7204779</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3853,7 +3857,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3863,7 +3867,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3874,6 +3878,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Mycket murken ved. Troligen gran</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3890,10 +3899,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934004</v>
+        <v>119933991</v>
       </c>
       <c r="B30" t="n">
-        <v>89650</v>
+        <v>86074</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3902,25 +3911,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>3294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3930,10 +3939,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>536620</v>
+        <v>536861</v>
       </c>
       <c r="R30" t="n">
-        <v>7204779</v>
+        <v>7204835</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3965,7 +3974,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3984,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3986,11 +3995,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Mycket murken ved. Troligen gran</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4007,10 +4011,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934252</v>
+        <v>119934078</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4023,21 +4027,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4047,10 +4051,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>536859</v>
+        <v>536606</v>
       </c>
       <c r="R31" t="n">
-        <v>7204833</v>
+        <v>7204748</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4082,7 +4086,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4092,7 +4096,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4119,10 +4123,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934137</v>
+        <v>119934208</v>
       </c>
       <c r="B32" t="n">
-        <v>74659</v>
+        <v>90576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4135,21 +4139,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4159,10 +4163,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>536837</v>
+        <v>536690</v>
       </c>
       <c r="R32" t="n">
-        <v>7204821</v>
+        <v>7204670</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4194,7 +4198,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4204,7 +4208,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4231,10 +4235,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934218</v>
+        <v>119934137</v>
       </c>
       <c r="B33" t="n">
-        <v>90594</v>
+        <v>74659</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,21 +4251,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4271,10 +4275,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>536789</v>
+        <v>536837</v>
       </c>
       <c r="R33" t="n">
-        <v>7204793</v>
+        <v>7204821</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4306,7 +4310,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4320,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4327,21 +4331,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4358,10 +4347,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934030</v>
+        <v>119934249</v>
       </c>
       <c r="B34" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4370,42 +4359,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långvikstjärnen, Njaka, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>536532</v>
+        <v>536683</v>
       </c>
       <c r="R34" t="n">
-        <v>7204362</v>
+        <v>7204683</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4437,7 +4422,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4447,7 +4432,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4474,10 +4459,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934114</v>
+        <v>119934250</v>
       </c>
       <c r="B35" t="n">
-        <v>94346</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,25 +4471,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4514,10 +4499,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>536852</v>
+        <v>536603</v>
       </c>
       <c r="R35" t="n">
-        <v>7204836</v>
+        <v>7204748</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4549,7 +4534,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,7 +4544,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4586,10 +4571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934251</v>
+        <v>119934216</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4602,21 +4587,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4626,10 +4611,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>536625</v>
+        <v>536769</v>
       </c>
       <c r="R36" t="n">
-        <v>7204790</v>
+        <v>7204825</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4661,7 +4646,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4671,7 +4656,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4713,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934249</v>
+        <v>119934080</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4729,21 +4714,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4753,10 +4738,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>536683</v>
+        <v>536865</v>
       </c>
       <c r="R37" t="n">
-        <v>7204683</v>
+        <v>7204832</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4788,7 +4773,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4798,7 +4783,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4825,10 +4810,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934184</v>
+        <v>119934066</v>
       </c>
       <c r="B38" t="n">
-        <v>94334</v>
+        <v>90527</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4837,25 +4822,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2809</v>
+        <v>112</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4865,10 +4850,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>536806</v>
+        <v>536771</v>
       </c>
       <c r="R38" t="n">
-        <v>7204783</v>
+        <v>7204791</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4900,7 +4885,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4910,7 +4895,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4921,6 +4906,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4937,10 +4937,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934214</v>
+        <v>119934252</v>
       </c>
       <c r="B39" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4953,21 +4953,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>536641</v>
+        <v>536859</v>
       </c>
       <c r="R39" t="n">
-        <v>7204731</v>
+        <v>7204833</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5049,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934215</v>
+        <v>119934079</v>
       </c>
       <c r="B40" t="n">
-        <v>90594</v>
+        <v>79624</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5065,21 +5065,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>536591</v>
+        <v>536847</v>
       </c>
       <c r="R40" t="n">
-        <v>7204751</v>
+        <v>7204825</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
